--- a/VerveStacks_CHE/vt_vervestacks_CHE_v1.xlsx
+++ b/VerveStacks_CHE/vt_vervestacks_CHE_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{96FC613B-639F-4FB3-A9D2-DB8253BCB4A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0F765A33-7222-4BC1-AEF1-4C308614183C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{60D9B660-A430-4878-BF63-1D544760D7C9}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{C4D657B9-F20B-49C1-803B-4FD80E5C1282}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -1250,7 +1250,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C22CEFF-7B64-458B-85A3-30912FEA7DC0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D128A4B-45C0-4764-B7CD-42BEBA8F6A56}">
   <dimension ref="B9:T31"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -2500,7 +2500,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{782B9C98-D685-4D5C-A433-F69E006D5635}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A315742E-411E-40A8-9272-BEB59C6F36FE}">
   <dimension ref="B9:T132"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -8271,7 +8271,7 @@
         <v>33</v>
       </c>
       <c r="L118">
-        <v>0.16852093340614119</v>
+        <v>0.16852093340614122</v>
       </c>
       <c r="N118" t="s">
         <v>139</v>

--- a/VerveStacks_CHE/vt_vervestacks_CHE_v1.xlsx
+++ b/VerveStacks_CHE/vt_vervestacks_CHE_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0F765A33-7222-4BC1-AEF1-4C308614183C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E1756FC9-D8B8-4E6B-9625-79886D04934C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{C4D657B9-F20B-49C1-803B-4FD80E5C1282}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{385DDBEF-8DB9-4CA6-ADB1-4BD0EB487FF6}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -1250,7 +1250,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D128A4B-45C0-4764-B7CD-42BEBA8F6A56}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D6E3624-A9AF-4304-A113-2C4443BB8313}">
   <dimension ref="B9:T31"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -2500,7 +2500,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A315742E-411E-40A8-9272-BEB59C6F36FE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CECBECE-52D7-425F-A12F-2969E99FFE65}">
   <dimension ref="B9:T132"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_CHE/vt_vervestacks_CHE_v1.xlsx
+++ b/VerveStacks_CHE/vt_vervestacks_CHE_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E1756FC9-D8B8-4E6B-9625-79886D04934C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{91AFA436-E699-4B1D-8B06-182146DB9E46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{385DDBEF-8DB9-4CA6-ADB1-4BD0EB487FF6}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{97FA9F02-C1BA-4563-9417-601FB69F97BD}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -1250,7 +1250,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D6E3624-A9AF-4304-A113-2C4443BB8313}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6918C270-0D60-495F-97FA-3DDA0A170497}">
   <dimension ref="B9:T31"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -2500,7 +2500,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CECBECE-52D7-425F-A12F-2969E99FFE65}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A88A03A6-6837-4B1A-BFB6-29D325A69C41}">
   <dimension ref="B9:T132"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_CHE/vt_vervestacks_CHE_v1.xlsx
+++ b/VerveStacks_CHE/vt_vervestacks_CHE_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{91AFA436-E699-4B1D-8B06-182146DB9E46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{104972E8-6AAB-4E83-8E86-364690BE8164}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{97FA9F02-C1BA-4563-9417-601FB69F97BD}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{05DB6096-7D0B-4E0F-9CEE-9A0A65D73A10}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -1250,7 +1250,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6918C270-0D60-495F-97FA-3DDA0A170497}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8261A3A6-A5BC-4F11-B371-FD394BDA5580}">
   <dimension ref="B9:T31"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -2500,7 +2500,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A88A03A6-6837-4B1A-BFB6-29D325A69C41}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A435F0B9-C0CE-44D1-8D8B-41EFF2ADB72C}">
   <dimension ref="B9:T132"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_CHE/vt_vervestacks_CHE_v1.xlsx
+++ b/VerveStacks_CHE/vt_vervestacks_CHE_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{104972E8-6AAB-4E83-8E86-364690BE8164}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7B0C60FD-98BF-4D9F-909F-50462029A08D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{05DB6096-7D0B-4E0F-9CEE-9A0A65D73A10}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{05D81881-54E4-4A0A-B33B-4F3A02BE10A1}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -1250,7 +1250,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8261A3A6-A5BC-4F11-B371-FD394BDA5580}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8EF691E-5016-4098-91DC-34A0DF0F2A2D}">
   <dimension ref="B9:T31"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -2500,7 +2500,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A435F0B9-C0CE-44D1-8D8B-41EFF2ADB72C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49BBDE75-D62F-4CFB-869E-7A94489D0BB3}">
   <dimension ref="B9:T132"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_CHE/vt_vervestacks_CHE_v1.xlsx
+++ b/VerveStacks_CHE/vt_vervestacks_CHE_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7B0C60FD-98BF-4D9F-909F-50462029A08D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E2EFAAC8-0D9C-4CEA-B8B1-99CD55FCBED1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{05D81881-54E4-4A0A-B33B-4F3A02BE10A1}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{DFC26D06-9651-4919-BBE5-2B2955EE5C6D}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -1250,7 +1250,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8EF691E-5016-4098-91DC-34A0DF0F2A2D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEBC12EF-EA33-417D-96D3-BBA65D0F34E0}">
   <dimension ref="B9:T31"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -2500,7 +2500,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49BBDE75-D62F-4CFB-869E-7A94489D0BB3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{621E5DD6-3255-4C04-A2BD-4EC4FC685CDC}">
   <dimension ref="B9:T132"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_CHE/vt_vervestacks_CHE_v1.xlsx
+++ b/VerveStacks_CHE/vt_vervestacks_CHE_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E2EFAAC8-0D9C-4CEA-B8B1-99CD55FCBED1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8F126955-6E1F-47DE-B1EC-FD5E4722AADD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{DFC26D06-9651-4919-BBE5-2B2955EE5C6D}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{E4F17B71-71CC-4D3A-92BA-52ECB6989DE7}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -1250,7 +1250,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEBC12EF-EA33-417D-96D3-BBA65D0F34E0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60B81362-E425-44A8-8BBA-EF64FB7551D0}">
   <dimension ref="B9:T31"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -2500,7 +2500,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{621E5DD6-3255-4C04-A2BD-4EC4FC685CDC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF8B50F1-69FE-44D5-ADB9-3BA3C43DA819}">
   <dimension ref="B9:T132"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_CHE/vt_vervestacks_CHE_v1.xlsx
+++ b/VerveStacks_CHE/vt_vervestacks_CHE_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8F126955-6E1F-47DE-B1EC-FD5E4722AADD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{020E52BD-7765-41DF-8B21-720B5D3A84F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{E4F17B71-71CC-4D3A-92BA-52ECB6989DE7}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{7168BAF0-00B8-451F-B6CF-A1A13CE78405}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -1250,7 +1250,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60B81362-E425-44A8-8BBA-EF64FB7551D0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F6764FE-7619-4AA8-94A2-22C6AA7C729A}">
   <dimension ref="B9:T31"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -2500,7 +2500,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF8B50F1-69FE-44D5-ADB9-3BA3C43DA819}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D2DBA35-ADDB-4E4D-AFD7-0C617CD56BBB}">
   <dimension ref="B9:T132"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_CHE/vt_vervestacks_CHE_v1.xlsx
+++ b/VerveStacks_CHE/vt_vervestacks_CHE_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{020E52BD-7765-41DF-8B21-720B5D3A84F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3FBFD989-1E80-4762-8E92-327EBA5C60B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{7168BAF0-00B8-451F-B6CF-A1A13CE78405}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{2D5DFB1F-EDE9-4A0D-9E92-601097C2AF70}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -426,7 +426,7 @@
     <t>ep_solar_pv_CHE</t>
   </si>
   <si>
-    <t>ep_windon_wind_c_won-CHE</t>
+    <t>ep_windon_wind_CHE</t>
   </si>
   <si>
     <t>windon</t>
@@ -1250,7 +1250,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F6764FE-7619-4AA8-94A2-22C6AA7C729A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBBBA3C4-DD86-40BC-B7C4-455B21A1312C}">
   <dimension ref="B9:T31"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -2500,7 +2500,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D2DBA35-ADDB-4E4D-AFD7-0C617CD56BBB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B391C513-E427-43DC-8D3F-D3C474585A0D}">
   <dimension ref="B9:T132"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -8271,7 +8271,7 @@
         <v>33</v>
       </c>
       <c r="L118">
-        <v>0.16852093340614122</v>
+        <v>0.17913988895703625</v>
       </c>
       <c r="N118" t="s">
         <v>139</v>
@@ -8327,7 +8327,7 @@
         <v>46</v>
       </c>
       <c r="L119">
-        <v>0.17657059999999999</v>
+        <v>0.17657060019791318</v>
       </c>
       <c r="N119" t="s">
         <v>139</v>
@@ -8383,7 +8383,7 @@
         <v>45</v>
       </c>
       <c r="L120">
-        <v>0.16076159100000001</v>
+        <v>0.17614020399124761</v>
       </c>
       <c r="N120" t="s">
         <v>139</v>
@@ -8439,7 +8439,7 @@
         <v>44</v>
       </c>
       <c r="L121">
-        <v>0.1664718266619718</v>
+        <v>0.17421176474617184</v>
       </c>
     </row>
     <row r="122" spans="2:20" x14ac:dyDescent="0.45">
@@ -8474,7 +8474,7 @@
         <v>43</v>
       </c>
       <c r="L122">
-        <v>0.17324086805384614</v>
+        <v>0.18216624634701162</v>
       </c>
     </row>
     <row r="123" spans="2:20" x14ac:dyDescent="0.45">
@@ -8509,7 +8509,7 @@
         <v>42</v>
       </c>
       <c r="L123">
-        <v>0.16042105172972976</v>
+        <v>0.17186478865517135</v>
       </c>
     </row>
     <row r="124" spans="2:20" x14ac:dyDescent="0.45">
@@ -8544,7 +8544,7 @@
         <v>41</v>
       </c>
       <c r="L124">
-        <v>0.15882470100000001</v>
+        <v>0.1751948590908658</v>
       </c>
     </row>
     <row r="125" spans="2:20" x14ac:dyDescent="0.45">
@@ -8579,7 +8579,7 @@
         <v>40</v>
       </c>
       <c r="L125">
-        <v>0.16504674365531916</v>
+        <v>0.1736774770610415</v>
       </c>
     </row>
     <row r="126" spans="2:20" x14ac:dyDescent="0.45">
@@ -8614,7 +8614,7 @@
         <v>39</v>
       </c>
       <c r="L126">
-        <v>0.16385107355440412</v>
+        <v>0.17312413828252077</v>
       </c>
     </row>
     <row r="127" spans="2:20" x14ac:dyDescent="0.45">
@@ -8649,7 +8649,7 @@
         <v>34</v>
       </c>
       <c r="L127">
-        <v>0.191499945</v>
+        <v>0.20930892224138253</v>
       </c>
     </row>
     <row r="128" spans="2:20" x14ac:dyDescent="0.45">
@@ -8672,7 +8672,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L128">
-        <v>0.10904849799999999</v>
+        <v>0.15124373474020081</v>
       </c>
     </row>
     <row r="129" spans="2:12" x14ac:dyDescent="0.45">
@@ -8695,7 +8695,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L129">
-        <v>2.2632488999999995E-2</v>
+        <v>2.2632488991967802E-2</v>
       </c>
     </row>
     <row r="130" spans="2:12" x14ac:dyDescent="0.45">
@@ -8718,7 +8718,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L130">
-        <v>0.10904849799999999</v>
+        <v>0.15124373474020081</v>
       </c>
     </row>
     <row r="131" spans="2:12" x14ac:dyDescent="0.45">
@@ -8741,7 +8741,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L131">
-        <v>8.3833751499999998E-2</v>
+        <v>0.12712443086902631</v>
       </c>
     </row>
     <row r="132" spans="2:12" x14ac:dyDescent="0.45">
@@ -8764,7 +8764,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L132">
-        <v>9.4605520999999998E-2</v>
+        <v>0.18337776500373579</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_CHE/vt_vervestacks_CHE_v1.xlsx
+++ b/VerveStacks_CHE/vt_vervestacks_CHE_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3FBFD989-1E80-4762-8E92-327EBA5C60B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2408250C-5896-4A05-BC58-6AE4AA5F2E35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{2D5DFB1F-EDE9-4A0D-9E92-601097C2AF70}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{9E457903-891A-4E69-8732-7B143CD957CF}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -1250,7 +1250,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBBBA3C4-DD86-40BC-B7C4-455B21A1312C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CDFBEF3-5306-4D03-B2CB-65958217C651}">
   <dimension ref="B9:T31"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -2500,7 +2500,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B391C513-E427-43DC-8D3F-D3C474585A0D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CF6826B-13BA-48EC-9144-B79AE2275CA2}">
   <dimension ref="B9:T132"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_CHE/vt_vervestacks_CHE_v1.xlsx
+++ b/VerveStacks_CHE/vt_vervestacks_CHE_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2408250C-5896-4A05-BC58-6AE4AA5F2E35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1EBC292A-8CC4-45CA-8964-9159392883D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{9E457903-891A-4E69-8732-7B143CD957CF}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{74BD9CD2-A642-48B5-9D07-F51F759C1456}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -1250,7 +1250,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CDFBEF3-5306-4D03-B2CB-65958217C651}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7859ADB6-7E07-454A-8409-8A04D31C8323}">
   <dimension ref="B9:T31"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -2500,7 +2500,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CF6826B-13BA-48EC-9144-B79AE2275CA2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17B0529D-AF53-4898-A5E6-999FD2F86122}">
   <dimension ref="B9:T132"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_CHE/vt_vervestacks_CHE_v1.xlsx
+++ b/VerveStacks_CHE/vt_vervestacks_CHE_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1EBC292A-8CC4-45CA-8964-9159392883D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3D547766-CDD4-46DD-A104-D9FD7485E691}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{74BD9CD2-A642-48B5-9D07-F51F759C1456}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{D033A8FB-AE56-4F80-8112-986AAC2A77F8}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -1250,7 +1250,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7859ADB6-7E07-454A-8409-8A04D31C8323}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DCAF01E-C627-433D-BB22-3CD9EE3A8DD0}">
   <dimension ref="B9:T31"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -2500,7 +2500,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17B0529D-AF53-4898-A5E6-999FD2F86122}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9946EE9B-657B-4173-B5AD-8D704464B176}">
   <dimension ref="B9:T132"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_CHE/vt_vervestacks_CHE_v1.xlsx
+++ b/VerveStacks_CHE/vt_vervestacks_CHE_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3D547766-CDD4-46DD-A104-D9FD7485E691}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{779A3ECB-15A7-4E31-982F-5FAA010C5697}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{D033A8FB-AE56-4F80-8112-986AAC2A77F8}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{9A1C369A-C625-4CA0-91A6-F3844E1B062B}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1407" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1197" uniqueCount="260">
   <si>
     <t>~fi_t</t>
   </si>
@@ -381,39 +381,6 @@
     <t>ep_nuclear_G100000500505</t>
   </si>
   <si>
-    <t>ep_oil_combined_cycle_G100000410168</t>
-  </si>
-  <si>
-    <t>oil</t>
-  </si>
-  <si>
-    <t>ep_oil_combined_cycle_G100001027890</t>
-  </si>
-  <si>
-    <t>ep_oil_gas_turbine_G100001020494__m</t>
-  </si>
-  <si>
-    <t>ep_oil_gas_turbine_G100001020500__m</t>
-  </si>
-  <si>
-    <t>ep_oil_gas_turbine_G100001020501__m</t>
-  </si>
-  <si>
-    <t>ep_oil_gas_turbine_G100001020502__m</t>
-  </si>
-  <si>
-    <t>ep_oil_gas_turbine_G100001020503__m</t>
-  </si>
-  <si>
-    <t>ep_oil_gas_turbine_G100001020504__m</t>
-  </si>
-  <si>
-    <t>ep_oil_gas_turbine_G100001020505__m</t>
-  </si>
-  <si>
-    <t>ep_oil_gas_turbine_G100001020506__m</t>
-  </si>
-  <si>
     <t>ep_solar_pv_</t>
   </si>
   <si>
@@ -817,36 +784,6 @@
   </si>
   <si>
     <t>ep_gas_gas_turbine_G100001020506__m_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_oil_combined_cycle_G100000410168_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_oil_combined_cycle_G100001027890_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_oil_gas_turbine_G100001020494__m_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_oil_gas_turbine_G100001020500__m_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_oil_gas_turbine_G100001020501__m_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_oil_gas_turbine_G100001020502__m_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_oil_gas_turbine_G100001020503__m_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_oil_gas_turbine_G100001020504__m_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_oil_gas_turbine_G100001020505__m_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_oil_gas_turbine_G100001020506__m_ccs-rf</t>
   </si>
   <si>
     <t>ccs retrofit of -- Monthey power station_1</t>
@@ -1250,8 +1187,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DCAF01E-C627-433D-BB22-3CD9EE3A8DD0}">
-  <dimension ref="B9:T31"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBC16623-6299-4454-85FA-8F168720885C}">
+  <dimension ref="B9:T21"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="9" spans="2:20" x14ac:dyDescent="0.45">
@@ -1259,7 +1196,7 @@
         <v>0</v>
       </c>
       <c r="N9" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
     </row>
     <row r="10" spans="2:20" x14ac:dyDescent="0.45">
@@ -1285,42 +1222,42 @@
         <v>9</v>
       </c>
       <c r="I10" t="s">
-        <v>246</v>
+        <v>235</v>
       </c>
       <c r="J10" t="s">
-        <v>247</v>
+        <v>236</v>
       </c>
       <c r="K10" t="s">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="L10" t="s">
         <v>10</v>
       </c>
       <c r="N10" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="O10" t="s">
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="Q10" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="R10" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="S10" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="T10" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
     </row>
     <row r="11" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
       <c r="C11" t="s">
         <v>16</v>
@@ -1353,30 +1290,30 @@
         <v>20</v>
       </c>
       <c r="N11" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O11" t="s">
+        <v>238</v>
+      </c>
+      <c r="P11" t="s">
         <v>249</v>
       </c>
-      <c r="P11" t="s">
-        <v>270</v>
-      </c>
       <c r="Q11" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R11" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S11" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T11" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
-        <v>250</v>
+        <v>239</v>
       </c>
       <c r="C12" t="s">
         <v>16</v>
@@ -1409,30 +1346,30 @@
         <v>20</v>
       </c>
       <c r="N12" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O12" t="s">
+        <v>239</v>
+      </c>
+      <c r="P12" t="s">
         <v>250</v>
       </c>
-      <c r="P12" t="s">
-        <v>271</v>
-      </c>
       <c r="Q12" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R12" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S12" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T12" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="C13" t="s">
         <v>16</v>
@@ -1465,30 +1402,30 @@
         <v>20</v>
       </c>
       <c r="N13" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O13" t="s">
+        <v>240</v>
+      </c>
+      <c r="P13" t="s">
         <v>251</v>
       </c>
-      <c r="P13" t="s">
-        <v>272</v>
-      </c>
       <c r="Q13" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R13" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S13" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T13" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="14" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="C14" t="s">
         <v>16</v>
@@ -1521,30 +1458,30 @@
         <v>20</v>
       </c>
       <c r="N14" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O14" t="s">
+        <v>241</v>
+      </c>
+      <c r="P14" t="s">
         <v>252</v>
       </c>
-      <c r="P14" t="s">
-        <v>273</v>
-      </c>
       <c r="Q14" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R14" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S14" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T14" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="C15" t="s">
         <v>16</v>
@@ -1577,30 +1514,30 @@
         <v>20</v>
       </c>
       <c r="N15" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O15" t="s">
+        <v>242</v>
+      </c>
+      <c r="P15" t="s">
         <v>253</v>
       </c>
-      <c r="P15" t="s">
-        <v>274</v>
-      </c>
       <c r="Q15" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R15" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S15" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T15" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="16" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="C16" t="s">
         <v>16</v>
@@ -1633,30 +1570,30 @@
         <v>20</v>
       </c>
       <c r="N16" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O16" t="s">
+        <v>243</v>
+      </c>
+      <c r="P16" t="s">
         <v>254</v>
       </c>
-      <c r="P16" t="s">
-        <v>275</v>
-      </c>
       <c r="Q16" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R16" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S16" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T16" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="17" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B17" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
       <c r="C17" t="s">
         <v>16</v>
@@ -1689,30 +1626,30 @@
         <v>20</v>
       </c>
       <c r="N17" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O17" t="s">
+        <v>244</v>
+      </c>
+      <c r="P17" t="s">
         <v>255</v>
       </c>
-      <c r="P17" t="s">
-        <v>276</v>
-      </c>
       <c r="Q17" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R17" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S17" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T17" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="18" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B18" t="s">
-        <v>256</v>
+        <v>245</v>
       </c>
       <c r="C18" t="s">
         <v>16</v>
@@ -1745,30 +1682,30 @@
         <v>20</v>
       </c>
       <c r="N18" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O18" t="s">
+        <v>245</v>
+      </c>
+      <c r="P18" t="s">
         <v>256</v>
       </c>
-      <c r="P18" t="s">
-        <v>277</v>
-      </c>
       <c r="Q18" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R18" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S18" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T18" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="19" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B19" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="C19" t="s">
         <v>16</v>
@@ -1801,30 +1738,30 @@
         <v>20</v>
       </c>
       <c r="N19" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O19" t="s">
+        <v>246</v>
+      </c>
+      <c r="P19" t="s">
         <v>257</v>
       </c>
-      <c r="P19" t="s">
-        <v>278</v>
-      </c>
       <c r="Q19" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R19" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S19" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T19" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="20" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B20" t="s">
-        <v>258</v>
+        <v>247</v>
       </c>
       <c r="C20" t="s">
         <v>16</v>
@@ -1857,30 +1794,30 @@
         <v>20</v>
       </c>
       <c r="N20" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O20" t="s">
+        <v>247</v>
+      </c>
+      <c r="P20" t="s">
         <v>258</v>
       </c>
-      <c r="P20" t="s">
-        <v>279</v>
-      </c>
       <c r="Q20" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R20" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S20" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T20" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="21" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B21" t="s">
-        <v>259</v>
+        <v>248</v>
       </c>
       <c r="C21" t="s">
         <v>16</v>
@@ -1913,585 +1850,25 @@
         <v>20</v>
       </c>
       <c r="N21" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O21" t="s">
+        <v>248</v>
+      </c>
+      <c r="P21" t="s">
         <v>259</v>
       </c>
-      <c r="P21" t="s">
-        <v>280</v>
-      </c>
       <c r="Q21" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R21" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S21" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T21" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="22" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B22" t="s">
-        <v>260</v>
-      </c>
-      <c r="C22" t="s">
-        <v>115</v>
-      </c>
-      <c r="D22" t="s">
-        <v>14</v>
-      </c>
-      <c r="E22">
-        <v>0.450625</v>
-      </c>
-      <c r="F22">
-        <v>1365</v>
-      </c>
-      <c r="G22">
-        <v>34.200000000000003</v>
-      </c>
-      <c r="H22">
-        <v>3.75</v>
-      </c>
-      <c r="I22">
-        <v>0.84455000000000002</v>
-      </c>
-      <c r="J22" t="s">
-        <v>114</v>
-      </c>
-      <c r="K22">
-        <v>1</v>
-      </c>
-      <c r="L22">
-        <v>20</v>
-      </c>
-      <c r="N22" t="s">
-        <v>139</v>
-      </c>
-      <c r="O22" t="s">
-        <v>260</v>
-      </c>
-      <c r="P22" t="s">
-        <v>270</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>141</v>
-      </c>
-      <c r="R22" t="s">
-        <v>142</v>
-      </c>
-      <c r="S22" t="s">
-        <v>143</v>
-      </c>
-      <c r="T22" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="23" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B23" t="s">
-        <v>261</v>
-      </c>
-      <c r="C23" t="s">
-        <v>115</v>
-      </c>
-      <c r="D23" t="s">
-        <v>14</v>
-      </c>
-      <c r="E23">
-        <v>0.35148750000000001</v>
-      </c>
-      <c r="F23">
-        <v>1365</v>
-      </c>
-      <c r="G23">
-        <v>34.200000000000003</v>
-      </c>
-      <c r="H23">
-        <v>3.75</v>
-      </c>
-      <c r="I23">
-        <v>0.84455000000000002</v>
-      </c>
-      <c r="J23" t="s">
-        <v>116</v>
-      </c>
-      <c r="K23">
-        <v>1</v>
-      </c>
-      <c r="L23">
-        <v>20</v>
-      </c>
-      <c r="N23" t="s">
-        <v>139</v>
-      </c>
-      <c r="O23" t="s">
-        <v>261</v>
-      </c>
-      <c r="P23" t="s">
-        <v>271</v>
-      </c>
-      <c r="Q23" t="s">
-        <v>141</v>
-      </c>
-      <c r="R23" t="s">
-        <v>142</v>
-      </c>
-      <c r="S23" t="s">
-        <v>143</v>
-      </c>
-      <c r="T23" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="24" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B24" t="s">
-        <v>262</v>
-      </c>
-      <c r="C24" t="s">
-        <v>115</v>
-      </c>
-      <c r="D24" t="s">
-        <v>14</v>
-      </c>
-      <c r="E24">
-        <v>0.27037500000000003</v>
-      </c>
-      <c r="F24">
-        <v>1365</v>
-      </c>
-      <c r="G24">
-        <v>34.200000000000003</v>
-      </c>
-      <c r="H24">
-        <v>3.75</v>
-      </c>
-      <c r="I24">
-        <v>0.84455000000000002</v>
-      </c>
-      <c r="J24" t="s">
-        <v>117</v>
-      </c>
-      <c r="K24">
-        <v>1</v>
-      </c>
-      <c r="L24">
-        <v>20</v>
-      </c>
-      <c r="N24" t="s">
-        <v>139</v>
-      </c>
-      <c r="O24" t="s">
-        <v>262</v>
-      </c>
-      <c r="P24" t="s">
-        <v>273</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>141</v>
-      </c>
-      <c r="R24" t="s">
-        <v>142</v>
-      </c>
-      <c r="S24" t="s">
-        <v>143</v>
-      </c>
-      <c r="T24" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="25" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B25" t="s">
-        <v>263</v>
-      </c>
-      <c r="C25" t="s">
-        <v>115</v>
-      </c>
-      <c r="D25" t="s">
-        <v>14</v>
-      </c>
-      <c r="E25">
-        <v>0.27037500000000003</v>
-      </c>
-      <c r="F25">
-        <v>1365</v>
-      </c>
-      <c r="G25">
-        <v>34.200000000000003</v>
-      </c>
-      <c r="H25">
-        <v>3.75</v>
-      </c>
-      <c r="I25">
-        <v>0.84455000000000002</v>
-      </c>
-      <c r="J25" t="s">
-        <v>118</v>
-      </c>
-      <c r="K25">
-        <v>1</v>
-      </c>
-      <c r="L25">
-        <v>20</v>
-      </c>
-      <c r="N25" t="s">
-        <v>139</v>
-      </c>
-      <c r="O25" t="s">
-        <v>263</v>
-      </c>
-      <c r="P25" t="s">
-        <v>274</v>
-      </c>
-      <c r="Q25" t="s">
-        <v>141</v>
-      </c>
-      <c r="R25" t="s">
-        <v>142</v>
-      </c>
-      <c r="S25" t="s">
-        <v>143</v>
-      </c>
-      <c r="T25" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="26" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B26" t="s">
-        <v>264</v>
-      </c>
-      <c r="C26" t="s">
-        <v>115</v>
-      </c>
-      <c r="D26" t="s">
-        <v>14</v>
-      </c>
-      <c r="E26">
-        <v>0.27037500000000003</v>
-      </c>
-      <c r="F26">
-        <v>1365</v>
-      </c>
-      <c r="G26">
-        <v>34.200000000000003</v>
-      </c>
-      <c r="H26">
-        <v>3.75</v>
-      </c>
-      <c r="I26">
-        <v>0.84455000000000002</v>
-      </c>
-      <c r="J26" t="s">
-        <v>119</v>
-      </c>
-      <c r="K26">
-        <v>1</v>
-      </c>
-      <c r="L26">
-        <v>20</v>
-      </c>
-      <c r="N26" t="s">
-        <v>139</v>
-      </c>
-      <c r="O26" t="s">
-        <v>264</v>
-      </c>
-      <c r="P26" t="s">
-        <v>275</v>
-      </c>
-      <c r="Q26" t="s">
-        <v>141</v>
-      </c>
-      <c r="R26" t="s">
-        <v>142</v>
-      </c>
-      <c r="S26" t="s">
-        <v>143</v>
-      </c>
-      <c r="T26" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="27" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B27" t="s">
-        <v>265</v>
-      </c>
-      <c r="C27" t="s">
-        <v>115</v>
-      </c>
-      <c r="D27" t="s">
-        <v>14</v>
-      </c>
-      <c r="E27">
-        <v>0.27037500000000003</v>
-      </c>
-      <c r="F27">
-        <v>1365</v>
-      </c>
-      <c r="G27">
-        <v>34.200000000000003</v>
-      </c>
-      <c r="H27">
-        <v>3.75</v>
-      </c>
-      <c r="I27">
-        <v>0.84455000000000002</v>
-      </c>
-      <c r="J27" t="s">
-        <v>120</v>
-      </c>
-      <c r="K27">
-        <v>1</v>
-      </c>
-      <c r="L27">
-        <v>20</v>
-      </c>
-      <c r="N27" t="s">
-        <v>139</v>
-      </c>
-      <c r="O27" t="s">
-        <v>265</v>
-      </c>
-      <c r="P27" t="s">
-        <v>276</v>
-      </c>
-      <c r="Q27" t="s">
-        <v>141</v>
-      </c>
-      <c r="R27" t="s">
-        <v>142</v>
-      </c>
-      <c r="S27" t="s">
-        <v>143</v>
-      </c>
-      <c r="T27" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="28" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B28" t="s">
-        <v>266</v>
-      </c>
-      <c r="C28" t="s">
-        <v>115</v>
-      </c>
-      <c r="D28" t="s">
-        <v>14</v>
-      </c>
-      <c r="E28">
-        <v>0.27037500000000003</v>
-      </c>
-      <c r="F28">
-        <v>1365</v>
-      </c>
-      <c r="G28">
-        <v>34.200000000000003</v>
-      </c>
-      <c r="H28">
-        <v>3.75</v>
-      </c>
-      <c r="I28">
-        <v>0.84455000000000002</v>
-      </c>
-      <c r="J28" t="s">
-        <v>121</v>
-      </c>
-      <c r="K28">
-        <v>1</v>
-      </c>
-      <c r="L28">
-        <v>20</v>
-      </c>
-      <c r="N28" t="s">
-        <v>139</v>
-      </c>
-      <c r="O28" t="s">
-        <v>266</v>
-      </c>
-      <c r="P28" t="s">
-        <v>277</v>
-      </c>
-      <c r="Q28" t="s">
-        <v>141</v>
-      </c>
-      <c r="R28" t="s">
-        <v>142</v>
-      </c>
-      <c r="S28" t="s">
-        <v>143</v>
-      </c>
-      <c r="T28" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="29" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B29" t="s">
-        <v>267</v>
-      </c>
-      <c r="C29" t="s">
-        <v>115</v>
-      </c>
-      <c r="D29" t="s">
-        <v>14</v>
-      </c>
-      <c r="E29">
-        <v>0.27037500000000003</v>
-      </c>
-      <c r="F29">
-        <v>1365</v>
-      </c>
-      <c r="G29">
-        <v>34.200000000000003</v>
-      </c>
-      <c r="H29">
-        <v>3.75</v>
-      </c>
-      <c r="I29">
-        <v>0.84455000000000002</v>
-      </c>
-      <c r="J29" t="s">
-        <v>122</v>
-      </c>
-      <c r="K29">
-        <v>1</v>
-      </c>
-      <c r="L29">
-        <v>20</v>
-      </c>
-      <c r="N29" t="s">
-        <v>139</v>
-      </c>
-      <c r="O29" t="s">
-        <v>267</v>
-      </c>
-      <c r="P29" t="s">
-        <v>278</v>
-      </c>
-      <c r="Q29" t="s">
-        <v>141</v>
-      </c>
-      <c r="R29" t="s">
-        <v>142</v>
-      </c>
-      <c r="S29" t="s">
-        <v>143</v>
-      </c>
-      <c r="T29" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="30" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B30" t="s">
-        <v>268</v>
-      </c>
-      <c r="C30" t="s">
-        <v>115</v>
-      </c>
-      <c r="D30" t="s">
-        <v>14</v>
-      </c>
-      <c r="E30">
-        <v>0.27037500000000003</v>
-      </c>
-      <c r="F30">
-        <v>1365</v>
-      </c>
-      <c r="G30">
-        <v>34.200000000000003</v>
-      </c>
-      <c r="H30">
-        <v>3.75</v>
-      </c>
-      <c r="I30">
-        <v>0.84455000000000002</v>
-      </c>
-      <c r="J30" t="s">
-        <v>123</v>
-      </c>
-      <c r="K30">
-        <v>1</v>
-      </c>
-      <c r="L30">
-        <v>20</v>
-      </c>
-      <c r="N30" t="s">
-        <v>139</v>
-      </c>
-      <c r="O30" t="s">
-        <v>268</v>
-      </c>
-      <c r="P30" t="s">
-        <v>279</v>
-      </c>
-      <c r="Q30" t="s">
-        <v>141</v>
-      </c>
-      <c r="R30" t="s">
-        <v>142</v>
-      </c>
-      <c r="S30" t="s">
-        <v>143</v>
-      </c>
-      <c r="T30" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="31" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B31" t="s">
-        <v>269</v>
-      </c>
-      <c r="C31" t="s">
-        <v>115</v>
-      </c>
-      <c r="D31" t="s">
-        <v>14</v>
-      </c>
-      <c r="E31">
-        <v>0.27037500000000003</v>
-      </c>
-      <c r="F31">
-        <v>1365</v>
-      </c>
-      <c r="G31">
-        <v>34.200000000000003</v>
-      </c>
-      <c r="H31">
-        <v>3.75</v>
-      </c>
-      <c r="I31">
-        <v>0.84455000000000002</v>
-      </c>
-      <c r="J31" t="s">
-        <v>124</v>
-      </c>
-      <c r="K31">
-        <v>1</v>
-      </c>
-      <c r="L31">
-        <v>20</v>
-      </c>
-      <c r="N31" t="s">
-        <v>139</v>
-      </c>
-      <c r="O31" t="s">
-        <v>269</v>
-      </c>
-      <c r="P31" t="s">
-        <v>280</v>
-      </c>
-      <c r="Q31" t="s">
-        <v>141</v>
-      </c>
-      <c r="R31" t="s">
-        <v>142</v>
-      </c>
-      <c r="S31" t="s">
-        <v>143</v>
-      </c>
-      <c r="T31" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
   </sheetData>
@@ -2500,8 +1877,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9946EE9B-657B-4173-B5AD-8D704464B176}">
-  <dimension ref="B9:T132"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DABA996F-C217-4655-8A8F-DBFDB8DED905}">
+  <dimension ref="B9:T122"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="9" spans="2:20" x14ac:dyDescent="0.45">
@@ -2509,7 +1886,7 @@
         <v>0</v>
       </c>
       <c r="N9" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
     </row>
     <row r="10" spans="2:20" x14ac:dyDescent="0.45">
@@ -2547,25 +1924,25 @@
         <v>11</v>
       </c>
       <c r="N10" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="O10" t="s">
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="Q10" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="R10" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="S10" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="T10" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
     </row>
     <row r="11" spans="2:20" x14ac:dyDescent="0.45">
@@ -2600,25 +1977,25 @@
         <v>50</v>
       </c>
       <c r="N11" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O11" t="s">
         <v>12</v>
       </c>
       <c r="P11" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="Q11" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R11" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S11" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T11" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12" spans="2:20" x14ac:dyDescent="0.45">
@@ -2653,25 +2030,25 @@
         <v>50</v>
       </c>
       <c r="N12" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O12" t="s">
         <v>15</v>
       </c>
       <c r="P12" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="Q12" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R12" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S12" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T12" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13" spans="2:20" x14ac:dyDescent="0.45">
@@ -2706,25 +2083,25 @@
         <v>50</v>
       </c>
       <c r="N13" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O13" t="s">
         <v>17</v>
       </c>
       <c r="P13" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="Q13" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R13" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S13" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T13" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="14" spans="2:20" x14ac:dyDescent="0.45">
@@ -2759,25 +2136,25 @@
         <v>50</v>
       </c>
       <c r="N14" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O14" t="s">
         <v>18</v>
       </c>
       <c r="P14" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="Q14" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R14" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S14" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T14" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15" spans="2:20" x14ac:dyDescent="0.45">
@@ -2812,25 +2189,25 @@
         <v>40</v>
       </c>
       <c r="N15" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O15" t="s">
         <v>19</v>
       </c>
       <c r="P15" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="Q15" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R15" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S15" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T15" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="16" spans="2:20" x14ac:dyDescent="0.45">
@@ -2865,25 +2242,25 @@
         <v>40</v>
       </c>
       <c r="N16" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O16" t="s">
         <v>20</v>
       </c>
       <c r="P16" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="Q16" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R16" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S16" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T16" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="17" spans="2:20" x14ac:dyDescent="0.45">
@@ -2918,25 +2295,25 @@
         <v>40</v>
       </c>
       <c r="N17" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O17" t="s">
         <v>21</v>
       </c>
       <c r="P17" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="Q17" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R17" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S17" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T17" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="18" spans="2:20" x14ac:dyDescent="0.45">
@@ -2971,25 +2348,25 @@
         <v>40</v>
       </c>
       <c r="N18" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O18" t="s">
         <v>22</v>
       </c>
       <c r="P18" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="Q18" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R18" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S18" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T18" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="19" spans="2:20" x14ac:dyDescent="0.45">
@@ -3024,25 +2401,25 @@
         <v>40</v>
       </c>
       <c r="N19" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O19" t="s">
         <v>23</v>
       </c>
       <c r="P19" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="Q19" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R19" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S19" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T19" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="20" spans="2:20" x14ac:dyDescent="0.45">
@@ -3077,25 +2454,25 @@
         <v>40</v>
       </c>
       <c r="N20" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O20" t="s">
         <v>24</v>
       </c>
       <c r="P20" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="Q20" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R20" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S20" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T20" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="21" spans="2:20" x14ac:dyDescent="0.45">
@@ -3130,25 +2507,25 @@
         <v>40</v>
       </c>
       <c r="N21" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O21" t="s">
         <v>25</v>
       </c>
       <c r="P21" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="Q21" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R21" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S21" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T21" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="22" spans="2:20" x14ac:dyDescent="0.45">
@@ -3183,25 +2560,25 @@
         <v>40</v>
       </c>
       <c r="N22" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O22" t="s">
         <v>26</v>
       </c>
       <c r="P22" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="Q22" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R22" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S22" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T22" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="23" spans="2:20" x14ac:dyDescent="0.45">
@@ -3236,25 +2613,25 @@
         <v>100</v>
       </c>
       <c r="N23" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O23" t="s">
         <v>27</v>
       </c>
       <c r="P23" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="Q23" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R23" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S23" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T23" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
     </row>
     <row r="24" spans="2:20" x14ac:dyDescent="0.45">
@@ -3289,25 +2666,25 @@
         <v>132</v>
       </c>
       <c r="N24" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O24" t="s">
         <v>29</v>
       </c>
       <c r="P24" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="Q24" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R24" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S24" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T24" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="25" spans="2:20" x14ac:dyDescent="0.45">
@@ -3342,25 +2719,25 @@
         <v>100</v>
       </c>
       <c r="N25" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O25" t="s">
         <v>30</v>
       </c>
       <c r="P25" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="Q25" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R25" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S25" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T25" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="26" spans="2:20" x14ac:dyDescent="0.45">
@@ -3395,25 +2772,25 @@
         <v>100</v>
       </c>
       <c r="N26" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O26" t="s">
         <v>31</v>
       </c>
       <c r="P26" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="Q26" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R26" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S26" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T26" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="27" spans="2:20" x14ac:dyDescent="0.45">
@@ -3448,25 +2825,25 @@
         <v>100</v>
       </c>
       <c r="N27" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O27" t="s">
         <v>32</v>
       </c>
       <c r="P27" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="Q27" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R27" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S27" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T27" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="28" spans="2:20" x14ac:dyDescent="0.45">
@@ -3501,25 +2878,25 @@
         <v>100</v>
       </c>
       <c r="N28" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O28" t="s">
         <v>33</v>
       </c>
       <c r="P28" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="Q28" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R28" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S28" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T28" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="29" spans="2:20" x14ac:dyDescent="0.45">
@@ -3554,25 +2931,25 @@
         <v>100</v>
       </c>
       <c r="N29" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O29" t="s">
         <v>34</v>
       </c>
       <c r="P29" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="Q29" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R29" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S29" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T29" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="30" spans="2:20" x14ac:dyDescent="0.45">
@@ -3607,25 +2984,25 @@
         <v>100</v>
       </c>
       <c r="N30" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O30" t="s">
         <v>35</v>
       </c>
       <c r="P30" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="Q30" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R30" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S30" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T30" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="31" spans="2:20" x14ac:dyDescent="0.45">
@@ -3660,25 +3037,25 @@
         <v>100</v>
       </c>
       <c r="N31" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O31" t="s">
         <v>36</v>
       </c>
       <c r="P31" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="Q31" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R31" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S31" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T31" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="32" spans="2:20" x14ac:dyDescent="0.45">
@@ -3713,25 +3090,25 @@
         <v>100</v>
       </c>
       <c r="N32" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O32" t="s">
         <v>37</v>
       </c>
       <c r="P32" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="Q32" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R32" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S32" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T32" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="33" spans="2:20" x14ac:dyDescent="0.45">
@@ -3766,25 +3143,25 @@
         <v>100</v>
       </c>
       <c r="N33" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O33" t="s">
         <v>38</v>
       </c>
       <c r="P33" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="Q33" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R33" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S33" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T33" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="34" spans="2:20" x14ac:dyDescent="0.45">
@@ -3819,25 +3196,25 @@
         <v>100</v>
       </c>
       <c r="N34" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O34" t="s">
         <v>39</v>
       </c>
       <c r="P34" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="Q34" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R34" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S34" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T34" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="35" spans="2:20" x14ac:dyDescent="0.45">
@@ -3872,25 +3249,25 @@
         <v>100</v>
       </c>
       <c r="N35" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O35" t="s">
         <v>40</v>
       </c>
       <c r="P35" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="Q35" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R35" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S35" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T35" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="36" spans="2:20" x14ac:dyDescent="0.45">
@@ -3925,25 +3302,25 @@
         <v>100</v>
       </c>
       <c r="N36" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O36" t="s">
         <v>41</v>
       </c>
       <c r="P36" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="Q36" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R36" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S36" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T36" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="37" spans="2:20" x14ac:dyDescent="0.45">
@@ -3978,25 +3355,25 @@
         <v>100</v>
       </c>
       <c r="N37" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O37" t="s">
         <v>42</v>
       </c>
       <c r="P37" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="Q37" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R37" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S37" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T37" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="38" spans="2:20" x14ac:dyDescent="0.45">
@@ -4031,25 +3408,25 @@
         <v>127</v>
       </c>
       <c r="N38" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O38" t="s">
         <v>43</v>
       </c>
       <c r="P38" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="Q38" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R38" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S38" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T38" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="39" spans="2:20" x14ac:dyDescent="0.45">
@@ -4084,25 +3461,25 @@
         <v>100</v>
       </c>
       <c r="N39" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O39" t="s">
         <v>44</v>
       </c>
       <c r="P39" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="Q39" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R39" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S39" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T39" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="40" spans="2:20" x14ac:dyDescent="0.45">
@@ -4137,25 +3514,25 @@
         <v>105</v>
       </c>
       <c r="N40" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O40" t="s">
         <v>45</v>
       </c>
       <c r="P40" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="Q40" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R40" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S40" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T40" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="41" spans="2:20" x14ac:dyDescent="0.45">
@@ -4190,25 +3567,25 @@
         <v>100</v>
       </c>
       <c r="N41" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O41" t="s">
         <v>46</v>
       </c>
       <c r="P41" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="Q41" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R41" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S41" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T41" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="42" spans="2:20" x14ac:dyDescent="0.45">
@@ -4243,25 +3620,25 @@
         <v>100</v>
       </c>
       <c r="N42" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O42" t="s">
         <v>47</v>
       </c>
       <c r="P42" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="Q42" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R42" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S42" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T42" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="43" spans="2:20" x14ac:dyDescent="0.45">
@@ -4296,25 +3673,25 @@
         <v>112</v>
       </c>
       <c r="N43" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O43" t="s">
         <v>48</v>
       </c>
       <c r="P43" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="Q43" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R43" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S43" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T43" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="44" spans="2:20" x14ac:dyDescent="0.45">
@@ -4349,25 +3726,25 @@
         <v>100</v>
       </c>
       <c r="N44" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O44" t="s">
         <v>49</v>
       </c>
       <c r="P44" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="Q44" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R44" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S44" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T44" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="45" spans="2:20" x14ac:dyDescent="0.45">
@@ -4402,25 +3779,25 @@
         <v>100</v>
       </c>
       <c r="N45" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O45" t="s">
         <v>50</v>
       </c>
       <c r="P45" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="Q45" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R45" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S45" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T45" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="46" spans="2:20" x14ac:dyDescent="0.45">
@@ -4455,25 +3832,25 @@
         <v>145</v>
       </c>
       <c r="N46" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O46" t="s">
         <v>51</v>
       </c>
       <c r="P46" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="Q46" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R46" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S46" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T46" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="47" spans="2:20" x14ac:dyDescent="0.45">
@@ -4508,25 +3885,25 @@
         <v>100</v>
       </c>
       <c r="N47" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O47" t="s">
         <v>52</v>
       </c>
       <c r="P47" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="Q47" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R47" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S47" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T47" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="48" spans="2:20" x14ac:dyDescent="0.45">
@@ -4561,25 +3938,25 @@
         <v>100</v>
       </c>
       <c r="N48" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O48" t="s">
         <v>53</v>
       </c>
       <c r="P48" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="Q48" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R48" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S48" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T48" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="49" spans="2:20" x14ac:dyDescent="0.45">
@@ -4614,25 +3991,25 @@
         <v>100</v>
       </c>
       <c r="N49" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O49" t="s">
         <v>54</v>
       </c>
       <c r="P49" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="Q49" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R49" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S49" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T49" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="50" spans="2:20" x14ac:dyDescent="0.45">
@@ -4667,25 +4044,25 @@
         <v>100</v>
       </c>
       <c r="N50" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O50" t="s">
         <v>55</v>
       </c>
       <c r="P50" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="Q50" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R50" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S50" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T50" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="51" spans="2:20" x14ac:dyDescent="0.45">
@@ -4720,25 +4097,25 @@
         <v>100</v>
       </c>
       <c r="N51" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O51" t="s">
         <v>56</v>
       </c>
       <c r="P51" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="Q51" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R51" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S51" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T51" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="52" spans="2:20" x14ac:dyDescent="0.45">
@@ -4773,25 +4150,25 @@
         <v>100</v>
       </c>
       <c r="N52" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O52" t="s">
         <v>57</v>
       </c>
       <c r="P52" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="Q52" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R52" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S52" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T52" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="53" spans="2:20" x14ac:dyDescent="0.45">
@@ -4826,25 +4203,25 @@
         <v>100</v>
       </c>
       <c r="N53" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O53" t="s">
         <v>58</v>
       </c>
       <c r="P53" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="Q53" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R53" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S53" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T53" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="54" spans="2:20" x14ac:dyDescent="0.45">
@@ -4879,25 +4256,25 @@
         <v>100</v>
       </c>
       <c r="N54" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O54" t="s">
         <v>59</v>
       </c>
       <c r="P54" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="Q54" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R54" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S54" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T54" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="55" spans="2:20" x14ac:dyDescent="0.45">
@@ -4932,25 +4309,25 @@
         <v>100</v>
       </c>
       <c r="N55" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O55" t="s">
         <v>60</v>
       </c>
       <c r="P55" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="Q55" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R55" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S55" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T55" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="56" spans="2:20" x14ac:dyDescent="0.45">
@@ -4985,25 +4362,25 @@
         <v>100</v>
       </c>
       <c r="N56" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O56" t="s">
         <v>61</v>
       </c>
       <c r="P56" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="Q56" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R56" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S56" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T56" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="57" spans="2:20" x14ac:dyDescent="0.45">
@@ -5038,25 +4415,25 @@
         <v>100</v>
       </c>
       <c r="N57" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O57" t="s">
         <v>62</v>
       </c>
       <c r="P57" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="Q57" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R57" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S57" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T57" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="58" spans="2:20" x14ac:dyDescent="0.45">
@@ -5091,25 +4468,25 @@
         <v>100</v>
       </c>
       <c r="N58" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O58" t="s">
         <v>63</v>
       </c>
       <c r="P58" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="Q58" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R58" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S58" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T58" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="59" spans="2:20" x14ac:dyDescent="0.45">
@@ -5144,25 +4521,25 @@
         <v>100</v>
       </c>
       <c r="N59" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O59" t="s">
         <v>64</v>
       </c>
       <c r="P59" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="Q59" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R59" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S59" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T59" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="60" spans="2:20" x14ac:dyDescent="0.45">
@@ -5197,25 +4574,25 @@
         <v>100</v>
       </c>
       <c r="N60" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O60" t="s">
         <v>65</v>
       </c>
       <c r="P60" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="Q60" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R60" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S60" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T60" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="61" spans="2:20" x14ac:dyDescent="0.45">
@@ -5250,25 +4627,25 @@
         <v>102</v>
       </c>
       <c r="N61" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O61" t="s">
         <v>66</v>
       </c>
       <c r="P61" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="Q61" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R61" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S61" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T61" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="62" spans="2:20" x14ac:dyDescent="0.45">
@@ -5303,25 +4680,25 @@
         <v>112</v>
       </c>
       <c r="N62" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O62" t="s">
         <v>67</v>
       </c>
       <c r="P62" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="Q62" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R62" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S62" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T62" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="63" spans="2:20" x14ac:dyDescent="0.45">
@@ -5356,25 +4733,25 @@
         <v>127</v>
       </c>
       <c r="N63" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O63" t="s">
         <v>68</v>
       </c>
       <c r="P63" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="Q63" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R63" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S63" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T63" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="64" spans="2:20" x14ac:dyDescent="0.45">
@@ -5409,25 +4786,25 @@
         <v>108</v>
       </c>
       <c r="N64" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O64" t="s">
         <v>69</v>
       </c>
       <c r="P64" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="Q64" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R64" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S64" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T64" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="65" spans="2:20" x14ac:dyDescent="0.45">
@@ -5462,25 +4839,25 @@
         <v>148</v>
       </c>
       <c r="N65" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O65" t="s">
         <v>70</v>
       </c>
       <c r="P65" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="Q65" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R65" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S65" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T65" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="66" spans="2:20" x14ac:dyDescent="0.45">
@@ -5515,25 +4892,25 @@
         <v>100</v>
       </c>
       <c r="N66" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O66" t="s">
         <v>71</v>
       </c>
       <c r="P66" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="Q66" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R66" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S66" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T66" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="67" spans="2:20" x14ac:dyDescent="0.45">
@@ -5568,25 +4945,25 @@
         <v>100</v>
       </c>
       <c r="N67" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O67" t="s">
         <v>72</v>
       </c>
       <c r="P67" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="Q67" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R67" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S67" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T67" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="68" spans="2:20" x14ac:dyDescent="0.45">
@@ -5621,25 +4998,25 @@
         <v>100</v>
       </c>
       <c r="N68" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O68" t="s">
         <v>73</v>
       </c>
       <c r="P68" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="Q68" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R68" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S68" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T68" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="69" spans="2:20" x14ac:dyDescent="0.45">
@@ -5674,25 +5051,25 @@
         <v>129</v>
       </c>
       <c r="N69" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O69" t="s">
         <v>74</v>
       </c>
       <c r="P69" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="Q69" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R69" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S69" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T69" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="70" spans="2:20" x14ac:dyDescent="0.45">
@@ -5727,25 +5104,25 @@
         <v>101</v>
       </c>
       <c r="N70" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O70" t="s">
         <v>75</v>
       </c>
       <c r="P70" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="Q70" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R70" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S70" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T70" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="71" spans="2:20" x14ac:dyDescent="0.45">
@@ -5780,25 +5157,25 @@
         <v>134</v>
       </c>
       <c r="N71" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O71" t="s">
         <v>76</v>
       </c>
       <c r="P71" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="Q71" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R71" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S71" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T71" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="72" spans="2:20" x14ac:dyDescent="0.45">
@@ -5833,25 +5210,25 @@
         <v>100</v>
       </c>
       <c r="N72" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O72" t="s">
         <v>77</v>
       </c>
       <c r="P72" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="Q72" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R72" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S72" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T72" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="73" spans="2:20" x14ac:dyDescent="0.45">
@@ -5886,25 +5263,25 @@
         <v>100</v>
       </c>
       <c r="N73" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O73" t="s">
         <v>78</v>
       </c>
       <c r="P73" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="Q73" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R73" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S73" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T73" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="74" spans="2:20" x14ac:dyDescent="0.45">
@@ -5939,25 +5316,25 @@
         <v>118</v>
       </c>
       <c r="N74" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="O74" t="s">
         <v>79</v>
       </c>
       <c r="P74" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="Q74" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R74" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S74" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T74" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="75" spans="2:20" x14ac:dyDescent="0.45">
@@ -5992,25 +5369,25 @@
         <v>100</v>
       </c>
       <c r="N75" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="O75" t="s">
         <v>80</v>
       </c>
       <c r="P75" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="Q75" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R75" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S75" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T75" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="76" spans="2:20" x14ac:dyDescent="0.45">
@@ -6045,25 +5422,25 @@
         <v>132</v>
       </c>
       <c r="N76" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="O76" t="s">
         <v>81</v>
       </c>
       <c r="P76" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="Q76" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R76" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S76" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T76" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="77" spans="2:20" x14ac:dyDescent="0.45">
@@ -6098,25 +5475,25 @@
         <v>100</v>
       </c>
       <c r="N77" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="O77" t="s">
         <v>82</v>
       </c>
       <c r="P77" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="Q77" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R77" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S77" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T77" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="78" spans="2:20" x14ac:dyDescent="0.45">
@@ -6151,25 +5528,25 @@
         <v>100</v>
       </c>
       <c r="N78" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="O78" t="s">
         <v>83</v>
       </c>
       <c r="P78" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="Q78" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R78" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S78" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T78" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="79" spans="2:20" x14ac:dyDescent="0.45">
@@ -6204,25 +5581,25 @@
         <v>100</v>
       </c>
       <c r="N79" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="O79" t="s">
         <v>84</v>
       </c>
       <c r="P79" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="Q79" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R79" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S79" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T79" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="80" spans="2:20" x14ac:dyDescent="0.45">
@@ -6257,25 +5634,25 @@
         <v>100</v>
       </c>
       <c r="N80" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="O80" t="s">
         <v>85</v>
       </c>
       <c r="P80" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="Q80" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R80" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S80" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T80" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="81" spans="2:20" x14ac:dyDescent="0.45">
@@ -6310,25 +5687,25 @@
         <v>100</v>
       </c>
       <c r="N81" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="O81" t="s">
         <v>86</v>
       </c>
       <c r="P81" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="Q81" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R81" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S81" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T81" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="82" spans="2:20" x14ac:dyDescent="0.45">
@@ -6363,25 +5740,25 @@
         <v>100</v>
       </c>
       <c r="N82" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="O82" t="s">
         <v>87</v>
       </c>
       <c r="P82" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="Q82" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R82" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S82" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T82" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="83" spans="2:20" x14ac:dyDescent="0.45">
@@ -6416,25 +5793,25 @@
         <v>100</v>
       </c>
       <c r="N83" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="O83" t="s">
         <v>88</v>
       </c>
       <c r="P83" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="Q83" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R83" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S83" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T83" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="84" spans="2:20" x14ac:dyDescent="0.45">
@@ -6469,25 +5846,25 @@
         <v>100</v>
       </c>
       <c r="N84" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="O84" t="s">
         <v>89</v>
       </c>
       <c r="P84" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="Q84" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R84" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S84" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T84" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="85" spans="2:20" x14ac:dyDescent="0.45">
@@ -6522,25 +5899,25 @@
         <v>100</v>
       </c>
       <c r="N85" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="O85" t="s">
         <v>90</v>
       </c>
       <c r="P85" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="Q85" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R85" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S85" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T85" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="86" spans="2:20" x14ac:dyDescent="0.45">
@@ -6575,25 +5952,25 @@
         <v>100</v>
       </c>
       <c r="N86" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="O86" t="s">
         <v>91</v>
       </c>
       <c r="P86" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="Q86" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R86" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S86" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T86" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="87" spans="2:20" x14ac:dyDescent="0.45">
@@ -6628,25 +6005,25 @@
         <v>100</v>
       </c>
       <c r="N87" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="O87" t="s">
         <v>92</v>
       </c>
       <c r="P87" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="Q87" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R87" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S87" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T87" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="88" spans="2:20" x14ac:dyDescent="0.45">
@@ -6681,25 +6058,25 @@
         <v>129</v>
       </c>
       <c r="N88" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="O88" t="s">
         <v>93</v>
       </c>
       <c r="P88" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="Q88" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R88" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S88" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T88" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="89" spans="2:20" x14ac:dyDescent="0.45">
@@ -6734,25 +6111,25 @@
         <v>100</v>
       </c>
       <c r="N89" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="O89" t="s">
         <v>94</v>
       </c>
       <c r="P89" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="Q89" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R89" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S89" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T89" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="90" spans="2:20" x14ac:dyDescent="0.45">
@@ -6787,25 +6164,25 @@
         <v>105</v>
       </c>
       <c r="N90" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O90" t="s">
         <v>95</v>
       </c>
       <c r="P90" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="Q90" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R90" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S90" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T90" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="91" spans="2:20" x14ac:dyDescent="0.45">
@@ -6840,25 +6217,25 @@
         <v>100</v>
       </c>
       <c r="N91" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O91" t="s">
         <v>96</v>
       </c>
       <c r="P91" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="Q91" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R91" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S91" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T91" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="92" spans="2:20" x14ac:dyDescent="0.45">
@@ -6893,25 +6270,25 @@
         <v>147</v>
       </c>
       <c r="N92" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O92" t="s">
         <v>97</v>
       </c>
       <c r="P92" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="Q92" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R92" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S92" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T92" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="93" spans="2:20" x14ac:dyDescent="0.45">
@@ -6946,25 +6323,25 @@
         <v>100</v>
       </c>
       <c r="N93" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O93" t="s">
         <v>98</v>
       </c>
       <c r="P93" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="Q93" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R93" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S93" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T93" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="94" spans="2:20" x14ac:dyDescent="0.45">
@@ -6999,25 +6376,25 @@
         <v>130</v>
       </c>
       <c r="N94" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O94" t="s">
         <v>99</v>
       </c>
       <c r="P94" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="Q94" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R94" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S94" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T94" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="95" spans="2:20" x14ac:dyDescent="0.45">
@@ -7052,25 +6429,25 @@
         <v>135</v>
       </c>
       <c r="N95" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O95" t="s">
         <v>100</v>
       </c>
       <c r="P95" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="Q95" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R95" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S95" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T95" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="96" spans="2:20" x14ac:dyDescent="0.45">
@@ -7105,25 +6482,25 @@
         <v>100</v>
       </c>
       <c r="N96" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O96" t="s">
         <v>101</v>
       </c>
       <c r="P96" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="Q96" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R96" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S96" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T96" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="97" spans="2:20" x14ac:dyDescent="0.45">
@@ -7158,25 +6535,25 @@
         <v>100</v>
       </c>
       <c r="N97" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O97" t="s">
         <v>102</v>
       </c>
       <c r="P97" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="Q97" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R97" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S97" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T97" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="98" spans="2:20" x14ac:dyDescent="0.45">
@@ -7211,25 +6588,25 @@
         <v>103</v>
       </c>
       <c r="N98" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O98" t="s">
         <v>103</v>
       </c>
       <c r="P98" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="Q98" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R98" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S98" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T98" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="99" spans="2:20" x14ac:dyDescent="0.45">
@@ -7264,25 +6641,25 @@
         <v>123</v>
       </c>
       <c r="N99" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O99" t="s">
         <v>104</v>
       </c>
       <c r="P99" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="Q99" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R99" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S99" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T99" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="100" spans="2:20" x14ac:dyDescent="0.45">
@@ -7317,25 +6694,25 @@
         <v>100</v>
       </c>
       <c r="N100" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O100" t="s">
         <v>105</v>
       </c>
       <c r="P100" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="Q100" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R100" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S100" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T100" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="101" spans="2:20" x14ac:dyDescent="0.45">
@@ -7370,25 +6747,25 @@
         <v>135</v>
       </c>
       <c r="N101" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O101" t="s">
         <v>106</v>
       </c>
       <c r="P101" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="Q101" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R101" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S101" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T101" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="102" spans="2:20" x14ac:dyDescent="0.45">
@@ -7423,25 +6800,25 @@
         <v>108</v>
       </c>
       <c r="N102" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O102" t="s">
         <v>107</v>
       </c>
       <c r="P102" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="Q102" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R102" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S102" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T102" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="103" spans="2:20" x14ac:dyDescent="0.45">
@@ -7476,25 +6853,25 @@
         <v>103</v>
       </c>
       <c r="N103" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O103" t="s">
         <v>108</v>
       </c>
       <c r="P103" t="s">
-        <v>238</v>
+        <v>227</v>
       </c>
       <c r="Q103" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R103" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S103" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T103" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="104" spans="2:20" x14ac:dyDescent="0.45">
@@ -7529,25 +6906,25 @@
         <v>71</v>
       </c>
       <c r="N104" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O104" t="s">
         <v>109</v>
       </c>
       <c r="P104" t="s">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="Q104" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R104" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S104" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T104" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="105" spans="2:20" x14ac:dyDescent="0.45">
@@ -7582,25 +6959,25 @@
         <v>76</v>
       </c>
       <c r="N105" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O105" t="s">
         <v>111</v>
       </c>
       <c r="P105" t="s">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="Q105" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R105" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S105" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T105" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="106" spans="2:20" x14ac:dyDescent="0.45">
@@ -7635,25 +7012,25 @@
         <v>86</v>
       </c>
       <c r="N106" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O106" t="s">
         <v>112</v>
       </c>
       <c r="P106" t="s">
-        <v>241</v>
+        <v>230</v>
       </c>
       <c r="Q106" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R106" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S106" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T106" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="107" spans="2:20" x14ac:dyDescent="0.45">
@@ -7688,25 +7065,25 @@
         <v>83</v>
       </c>
       <c r="N107" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O107" t="s">
         <v>113</v>
       </c>
       <c r="P107" t="s">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="Q107" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R107" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S107" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="T107" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="108" spans="2:20" x14ac:dyDescent="0.45">
@@ -7717,102 +7094,108 @@
         <v>115</v>
       </c>
       <c r="D108" t="s">
-        <v>14</v>
+        <v>116</v>
       </c>
       <c r="E108">
-        <v>2009</v>
+        <v>2022</v>
       </c>
       <c r="F108">
-        <v>5.5E-2</v>
+        <v>4.4311999999999996</v>
       </c>
       <c r="G108">
-        <v>0.51500000000000001</v>
+        <v>1</v>
       </c>
       <c r="H108">
-        <v>1391.5</v>
+        <v>990</v>
       </c>
       <c r="I108">
-        <v>42.35</v>
+        <v>16.5</v>
       </c>
       <c r="J108">
-        <v>4.0425000000000004</v>
+        <v>0</v>
       </c>
       <c r="K108">
-        <v>50</v>
+        <v>33</v>
+      </c>
+      <c r="L108">
+        <v>0.17913988895703625</v>
       </c>
       <c r="N108" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O108" t="s">
         <v>114</v>
       </c>
       <c r="P108" t="s">
-        <v>146</v>
+        <v>232</v>
       </c>
       <c r="Q108" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R108" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S108" t="s">
-        <v>143</v>
+        <v>233</v>
       </c>
       <c r="T108" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
     </row>
     <row r="109" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B109" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C109" t="s">
         <v>115</v>
       </c>
       <c r="D109" t="s">
-        <v>14</v>
+        <v>116</v>
       </c>
       <c r="E109">
-        <v>1988</v>
+        <v>2009</v>
       </c>
       <c r="F109">
-        <v>4.3799999999999999E-2</v>
+        <v>1.5E-3</v>
       </c>
       <c r="G109">
-        <v>0.4017</v>
+        <v>1</v>
       </c>
       <c r="H109">
-        <v>1633.5000000000002</v>
+        <v>1336.5</v>
       </c>
       <c r="I109">
-        <v>50.050000000000004</v>
+        <v>21.450000000000003</v>
       </c>
       <c r="J109">
-        <v>4.41</v>
+        <v>0</v>
       </c>
       <c r="K109">
-        <v>50</v>
+        <v>46</v>
+      </c>
+      <c r="L109">
+        <v>0.17657060019791318</v>
       </c>
       <c r="N109" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O109" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P109" t="s">
-        <v>148</v>
+        <v>234</v>
       </c>
       <c r="Q109" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R109" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S109" t="s">
-        <v>143</v>
+        <v>233</v>
       </c>
       <c r="T109" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
     </row>
     <row r="110" spans="2:20" x14ac:dyDescent="0.45">
@@ -7823,947 +7206,411 @@
         <v>115</v>
       </c>
       <c r="D110" t="s">
-        <v>14</v>
+        <v>116</v>
       </c>
       <c r="E110">
-        <v>2023</v>
+        <v>2010</v>
       </c>
       <c r="F110">
-        <v>3.1300000000000001E-2</v>
+        <v>2.3999999999999998E-3</v>
       </c>
       <c r="G110">
-        <v>0.309</v>
+        <v>1</v>
       </c>
       <c r="H110">
         <v>1336.5</v>
       </c>
       <c r="I110">
-        <v>31.460000000000004</v>
+        <v>21.450000000000003</v>
       </c>
       <c r="J110">
-        <v>5.67</v>
+        <v>0</v>
       </c>
       <c r="K110">
-        <v>40</v>
+        <v>45</v>
+      </c>
+      <c r="L110">
+        <v>0.17614020399124761</v>
       </c>
       <c r="N110" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="O110" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="P110" t="s">
-        <v>149</v>
+        <v>234</v>
       </c>
       <c r="Q110" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="R110" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="S110" t="s">
-        <v>143</v>
+        <v>233</v>
       </c>
       <c r="T110" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
     </row>
     <row r="111" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B111" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C111" t="s">
         <v>115</v>
       </c>
       <c r="D111" t="s">
-        <v>14</v>
+        <v>116</v>
       </c>
       <c r="E111">
-        <v>2023</v>
+        <v>2011</v>
       </c>
       <c r="F111">
-        <v>3.1300000000000001E-2</v>
+        <v>7.1000000000000013E-3</v>
       </c>
       <c r="G111">
-        <v>0.309</v>
+        <v>1</v>
       </c>
       <c r="H111">
-        <v>1336.5</v>
+        <v>1336.4999999999998</v>
       </c>
       <c r="I111">
-        <v>31.460000000000004</v>
+        <v>21.45</v>
       </c>
       <c r="J111">
-        <v>5.67</v>
+        <v>0</v>
       </c>
       <c r="K111">
-        <v>40</v>
-      </c>
-      <c r="N111" t="s">
-        <v>139</v>
-      </c>
-      <c r="O111" t="s">
-        <v>118</v>
-      </c>
-      <c r="P111" t="s">
-        <v>150</v>
-      </c>
-      <c r="Q111" t="s">
-        <v>141</v>
-      </c>
-      <c r="R111" t="s">
-        <v>142</v>
-      </c>
-      <c r="S111" t="s">
-        <v>143</v>
-      </c>
-      <c r="T111" t="s">
-        <v>147</v>
+        <v>44</v>
+      </c>
+      <c r="L111">
+        <v>0.17421176474617184</v>
       </c>
     </row>
     <row r="112" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B112" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C112" t="s">
         <v>115</v>
       </c>
       <c r="D112" t="s">
-        <v>14</v>
+        <v>116</v>
       </c>
       <c r="E112">
-        <v>2023</v>
+        <v>2012</v>
       </c>
       <c r="F112">
-        <v>3.1300000000000001E-2</v>
+        <v>2.5999999999999999E-2</v>
       </c>
       <c r="G112">
-        <v>0.309</v>
+        <v>1</v>
       </c>
       <c r="H112">
         <v>1336.5</v>
       </c>
       <c r="I112">
-        <v>31.460000000000004</v>
+        <v>21.450000000000003</v>
       </c>
       <c r="J112">
-        <v>5.67</v>
+        <v>0</v>
       </c>
       <c r="K112">
-        <v>40</v>
-      </c>
-      <c r="N112" t="s">
-        <v>139</v>
-      </c>
-      <c r="O112" t="s">
-        <v>119</v>
-      </c>
-      <c r="P112" t="s">
-        <v>151</v>
-      </c>
-      <c r="Q112" t="s">
-        <v>141</v>
-      </c>
-      <c r="R112" t="s">
-        <v>142</v>
-      </c>
-      <c r="S112" t="s">
-        <v>143</v>
-      </c>
-      <c r="T112" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="113" spans="2:20" x14ac:dyDescent="0.45">
+        <v>43</v>
+      </c>
+      <c r="L112">
+        <v>0.18216624634701162</v>
+      </c>
+    </row>
+    <row r="113" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B113" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C113" t="s">
         <v>115</v>
       </c>
       <c r="D113" t="s">
-        <v>14</v>
+        <v>116</v>
       </c>
       <c r="E113">
-        <v>2023</v>
+        <v>2013</v>
       </c>
       <c r="F113">
-        <v>3.1300000000000001E-2</v>
+        <v>1.4799999999999999E-2</v>
       </c>
       <c r="G113">
-        <v>0.309</v>
+        <v>1</v>
       </c>
       <c r="H113">
-        <v>1336.5</v>
+        <v>1336.5000000000002</v>
       </c>
       <c r="I113">
-        <v>31.460000000000004</v>
+        <v>21.450000000000003</v>
       </c>
       <c r="J113">
-        <v>5.67</v>
+        <v>0</v>
       </c>
       <c r="K113">
-        <v>40</v>
-      </c>
-      <c r="N113" t="s">
-        <v>139</v>
-      </c>
-      <c r="O113" t="s">
-        <v>120</v>
-      </c>
-      <c r="P113" t="s">
-        <v>152</v>
-      </c>
-      <c r="Q113" t="s">
-        <v>141</v>
-      </c>
-      <c r="R113" t="s">
-        <v>142</v>
-      </c>
-      <c r="S113" t="s">
-        <v>143</v>
-      </c>
-      <c r="T113" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="114" spans="2:20" x14ac:dyDescent="0.45">
+        <v>42</v>
+      </c>
+      <c r="L113">
+        <v>0.17186478865517135</v>
+      </c>
+    </row>
+    <row r="114" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B114" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C114" t="s">
         <v>115</v>
       </c>
       <c r="D114" t="s">
-        <v>14</v>
+        <v>116</v>
       </c>
       <c r="E114">
-        <v>2023</v>
+        <v>2014</v>
       </c>
       <c r="F114">
-        <v>3.1300000000000001E-2</v>
+        <v>1E-3</v>
       </c>
       <c r="G114">
-        <v>0.309</v>
+        <v>1</v>
       </c>
       <c r="H114">
         <v>1336.5</v>
       </c>
       <c r="I114">
-        <v>31.460000000000004</v>
+        <v>21.450000000000003</v>
       </c>
       <c r="J114">
-        <v>5.67</v>
+        <v>0</v>
       </c>
       <c r="K114">
-        <v>40</v>
-      </c>
-      <c r="N114" t="s">
-        <v>139</v>
-      </c>
-      <c r="O114" t="s">
-        <v>121</v>
-      </c>
-      <c r="P114" t="s">
-        <v>153</v>
-      </c>
-      <c r="Q114" t="s">
-        <v>141</v>
-      </c>
-      <c r="R114" t="s">
-        <v>142</v>
-      </c>
-      <c r="S114" t="s">
-        <v>143</v>
-      </c>
-      <c r="T114" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="115" spans="2:20" x14ac:dyDescent="0.45">
+        <v>41</v>
+      </c>
+      <c r="L114">
+        <v>0.1751948590908658</v>
+      </c>
+    </row>
+    <row r="115" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B115" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C115" t="s">
         <v>115</v>
       </c>
       <c r="D115" t="s">
-        <v>14</v>
+        <v>116</v>
       </c>
       <c r="E115">
-        <v>2023</v>
+        <v>2015</v>
       </c>
       <c r="F115">
-        <v>3.1300000000000001E-2</v>
+        <v>2.3500000000000004E-2</v>
       </c>
       <c r="G115">
-        <v>0.309</v>
+        <v>1</v>
       </c>
       <c r="H115">
         <v>1336.5</v>
       </c>
       <c r="I115">
-        <v>31.460000000000004</v>
+        <v>21.450000000000003</v>
       </c>
       <c r="J115">
-        <v>5.67</v>
+        <v>0</v>
       </c>
       <c r="K115">
         <v>40</v>
       </c>
-      <c r="N115" t="s">
-        <v>139</v>
-      </c>
-      <c r="O115" t="s">
-        <v>122</v>
-      </c>
-      <c r="P115" t="s">
-        <v>154</v>
-      </c>
-      <c r="Q115" t="s">
-        <v>141</v>
-      </c>
-      <c r="R115" t="s">
-        <v>142</v>
-      </c>
-      <c r="S115" t="s">
-        <v>143</v>
-      </c>
-      <c r="T115" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="116" spans="2:20" x14ac:dyDescent="0.45">
+      <c r="L115">
+        <v>0.1736774770610415</v>
+      </c>
+    </row>
+    <row r="116" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B116" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C116" t="s">
         <v>115</v>
       </c>
       <c r="D116" t="s">
-        <v>14</v>
+        <v>116</v>
       </c>
       <c r="E116">
-        <v>2023</v>
+        <v>2016</v>
       </c>
       <c r="F116">
-        <v>3.1300000000000001E-2</v>
+        <v>1.9300000000000005E-2</v>
       </c>
       <c r="G116">
-        <v>0.309</v>
+        <v>1</v>
       </c>
       <c r="H116">
         <v>1336.5</v>
       </c>
       <c r="I116">
-        <v>31.460000000000004</v>
+        <v>21.450000000000003</v>
       </c>
       <c r="J116">
-        <v>5.67</v>
+        <v>0</v>
       </c>
       <c r="K116">
-        <v>40</v>
-      </c>
-      <c r="N116" t="s">
-        <v>139</v>
-      </c>
-      <c r="O116" t="s">
-        <v>123</v>
-      </c>
-      <c r="P116" t="s">
-        <v>155</v>
-      </c>
-      <c r="Q116" t="s">
-        <v>141</v>
-      </c>
-      <c r="R116" t="s">
-        <v>142</v>
-      </c>
-      <c r="S116" t="s">
-        <v>143</v>
-      </c>
-      <c r="T116" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="117" spans="2:20" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+      <c r="L116">
+        <v>0.17312413828252077</v>
+      </c>
+    </row>
+    <row r="117" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B117" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="C117" t="s">
         <v>115</v>
       </c>
       <c r="D117" t="s">
-        <v>14</v>
+        <v>116</v>
       </c>
       <c r="E117">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="F117">
-        <v>3.1300000000000001E-2</v>
+        <v>1.1999999999999999E-3</v>
       </c>
       <c r="G117">
-        <v>0.309</v>
+        <v>1</v>
       </c>
       <c r="H117">
         <v>1336.5</v>
       </c>
       <c r="I117">
-        <v>31.460000000000004</v>
+        <v>21.450000000000003</v>
       </c>
       <c r="J117">
-        <v>5.67</v>
+        <v>0</v>
       </c>
       <c r="K117">
-        <v>40</v>
-      </c>
-      <c r="N117" t="s">
-        <v>139</v>
-      </c>
-      <c r="O117" t="s">
-        <v>124</v>
-      </c>
-      <c r="P117" t="s">
-        <v>156</v>
-      </c>
-      <c r="Q117" t="s">
-        <v>141</v>
-      </c>
-      <c r="R117" t="s">
-        <v>142</v>
-      </c>
-      <c r="S117" t="s">
-        <v>143</v>
-      </c>
-      <c r="T117" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="118" spans="2:20" x14ac:dyDescent="0.45">
+        <v>34</v>
+      </c>
+      <c r="L117">
+        <v>0.20930892224138253</v>
+      </c>
+    </row>
+    <row r="118" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B118" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="C118" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="D118" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="E118">
+        <v>2010</v>
+      </c>
+      <c r="F118">
+        <v>1.6E-2</v>
+      </c>
+      <c r="G118">
+        <v>0.33123000000000002</v>
+      </c>
+      <c r="L118">
+        <v>0.15124373474020081</v>
+      </c>
+    </row>
+    <row r="119" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B119" t="s">
+        <v>118</v>
+      </c>
+      <c r="C119" t="s">
+        <v>119</v>
+      </c>
+      <c r="D119" t="s">
+        <v>120</v>
+      </c>
+      <c r="E119">
+        <v>2015</v>
+      </c>
+      <c r="F119">
+        <v>1.2E-2</v>
+      </c>
+      <c r="G119">
+        <v>0.33123000000000002</v>
+      </c>
+      <c r="L119">
+        <v>2.2632488991967802E-2</v>
+      </c>
+    </row>
+    <row r="120" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B120" t="s">
+        <v>118</v>
+      </c>
+      <c r="C120" t="s">
+        <v>119</v>
+      </c>
+      <c r="D120" t="s">
+        <v>120</v>
+      </c>
+      <c r="E120">
+        <v>2016</v>
+      </c>
+      <c r="F120">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="G120">
+        <v>0.33123000000000002</v>
+      </c>
+      <c r="L120">
+        <v>0.15124373474020081</v>
+      </c>
+    </row>
+    <row r="121" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B121" t="s">
+        <v>118</v>
+      </c>
+      <c r="C121" t="s">
+        <v>119</v>
+      </c>
+      <c r="D121" t="s">
+        <v>120</v>
+      </c>
+      <c r="E121">
         <v>2022</v>
       </c>
-      <c r="F118">
-        <v>4.4311999999999996</v>
-      </c>
-      <c r="G118">
-        <v>1</v>
-      </c>
-      <c r="H118">
-        <v>990</v>
-      </c>
-      <c r="I118">
-        <v>16.5</v>
-      </c>
-      <c r="J118">
-        <v>0</v>
-      </c>
-      <c r="K118">
-        <v>33</v>
-      </c>
-      <c r="L118">
-        <v>0.17913988895703625</v>
-      </c>
-      <c r="N118" t="s">
-        <v>139</v>
-      </c>
-      <c r="O118" t="s">
-        <v>125</v>
-      </c>
-      <c r="P118" t="s">
-        <v>243</v>
-      </c>
-      <c r="Q118" t="s">
-        <v>141</v>
-      </c>
-      <c r="R118" t="s">
-        <v>142</v>
-      </c>
-      <c r="S118" t="s">
-        <v>244</v>
-      </c>
-      <c r="T118" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="119" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B119" t="s">
-        <v>128</v>
-      </c>
-      <c r="C119" t="s">
-        <v>126</v>
-      </c>
-      <c r="D119" t="s">
-        <v>127</v>
-      </c>
-      <c r="E119">
-        <v>2009</v>
-      </c>
-      <c r="F119">
-        <v>1.5E-3</v>
-      </c>
-      <c r="G119">
-        <v>1</v>
-      </c>
-      <c r="H119">
-        <v>1336.5</v>
-      </c>
-      <c r="I119">
-        <v>21.450000000000003</v>
-      </c>
-      <c r="J119">
-        <v>0</v>
-      </c>
-      <c r="K119">
-        <v>46</v>
-      </c>
-      <c r="L119">
-        <v>0.17657060019791318</v>
-      </c>
-      <c r="N119" t="s">
-        <v>139</v>
-      </c>
-      <c r="O119" t="s">
-        <v>128</v>
-      </c>
-      <c r="P119" t="s">
-        <v>245</v>
-      </c>
-      <c r="Q119" t="s">
-        <v>141</v>
-      </c>
-      <c r="R119" t="s">
-        <v>142</v>
-      </c>
-      <c r="S119" t="s">
-        <v>244</v>
-      </c>
-      <c r="T119" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="120" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B120" t="s">
-        <v>128</v>
-      </c>
-      <c r="C120" t="s">
-        <v>126</v>
-      </c>
-      <c r="D120" t="s">
-        <v>127</v>
-      </c>
-      <c r="E120">
-        <v>2010</v>
-      </c>
-      <c r="F120">
-        <v>2.3999999999999998E-3</v>
-      </c>
-      <c r="G120">
-        <v>1</v>
-      </c>
-      <c r="H120">
-        <v>1336.5</v>
-      </c>
-      <c r="I120">
-        <v>21.450000000000003</v>
-      </c>
-      <c r="J120">
-        <v>0</v>
-      </c>
-      <c r="K120">
-        <v>45</v>
-      </c>
-      <c r="L120">
-        <v>0.17614020399124761</v>
-      </c>
-      <c r="N120" t="s">
-        <v>139</v>
-      </c>
-      <c r="O120" t="s">
-        <v>129</v>
-      </c>
-      <c r="P120" t="s">
-        <v>245</v>
-      </c>
-      <c r="Q120" t="s">
-        <v>141</v>
-      </c>
-      <c r="R120" t="s">
-        <v>142</v>
-      </c>
-      <c r="S120" t="s">
-        <v>244</v>
-      </c>
-      <c r="T120" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="121" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B121" t="s">
-        <v>128</v>
-      </c>
-      <c r="C121" t="s">
-        <v>126</v>
-      </c>
-      <c r="D121" t="s">
-        <v>127</v>
-      </c>
-      <c r="E121">
-        <v>2011</v>
-      </c>
       <c r="F121">
-        <v>7.1000000000000013E-3</v>
+        <v>4.6999999999999993E-2</v>
       </c>
       <c r="G121">
-        <v>1</v>
-      </c>
-      <c r="H121">
-        <v>1336.4999999999998</v>
-      </c>
-      <c r="I121">
-        <v>21.45</v>
-      </c>
-      <c r="J121">
-        <v>0</v>
-      </c>
-      <c r="K121">
-        <v>44</v>
+        <v>0.33123000000000002</v>
       </c>
       <c r="L121">
-        <v>0.17421176474617184</v>
-      </c>
-    </row>
-    <row r="122" spans="2:20" x14ac:dyDescent="0.45">
+        <v>0.12712443086902631</v>
+      </c>
+    </row>
+    <row r="122" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B122" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="C122" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="D122" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="E122">
-        <v>2012</v>
+        <v>2023</v>
       </c>
       <c r="F122">
-        <v>2.5999999999999999E-2</v>
+        <v>1.4E-2</v>
       </c>
       <c r="G122">
-        <v>1</v>
-      </c>
-      <c r="H122">
-        <v>1336.5</v>
-      </c>
-      <c r="I122">
-        <v>21.450000000000003</v>
-      </c>
-      <c r="J122">
-        <v>0</v>
-      </c>
-      <c r="K122">
-        <v>43</v>
+        <v>0.33123000000000002</v>
       </c>
       <c r="L122">
-        <v>0.18216624634701162</v>
-      </c>
-    </row>
-    <row r="123" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B123" t="s">
-        <v>128</v>
-      </c>
-      <c r="C123" t="s">
-        <v>126</v>
-      </c>
-      <c r="D123" t="s">
-        <v>127</v>
-      </c>
-      <c r="E123">
-        <v>2013</v>
-      </c>
-      <c r="F123">
-        <v>1.4799999999999999E-2</v>
-      </c>
-      <c r="G123">
-        <v>1</v>
-      </c>
-      <c r="H123">
-        <v>1336.5000000000002</v>
-      </c>
-      <c r="I123">
-        <v>21.450000000000003</v>
-      </c>
-      <c r="J123">
-        <v>0</v>
-      </c>
-      <c r="K123">
-        <v>42</v>
-      </c>
-      <c r="L123">
-        <v>0.17186478865517135</v>
-      </c>
-    </row>
-    <row r="124" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B124" t="s">
-        <v>128</v>
-      </c>
-      <c r="C124" t="s">
-        <v>126</v>
-      </c>
-      <c r="D124" t="s">
-        <v>127</v>
-      </c>
-      <c r="E124">
-        <v>2014</v>
-      </c>
-      <c r="F124">
-        <v>1E-3</v>
-      </c>
-      <c r="G124">
-        <v>1</v>
-      </c>
-      <c r="H124">
-        <v>1336.5</v>
-      </c>
-      <c r="I124">
-        <v>21.450000000000003</v>
-      </c>
-      <c r="J124">
-        <v>0</v>
-      </c>
-      <c r="K124">
-        <v>41</v>
-      </c>
-      <c r="L124">
-        <v>0.1751948590908658</v>
-      </c>
-    </row>
-    <row r="125" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B125" t="s">
-        <v>128</v>
-      </c>
-      <c r="C125" t="s">
-        <v>126</v>
-      </c>
-      <c r="D125" t="s">
-        <v>127</v>
-      </c>
-      <c r="E125">
-        <v>2015</v>
-      </c>
-      <c r="F125">
-        <v>2.3500000000000004E-2</v>
-      </c>
-      <c r="G125">
-        <v>1</v>
-      </c>
-      <c r="H125">
-        <v>1336.5</v>
-      </c>
-      <c r="I125">
-        <v>21.450000000000003</v>
-      </c>
-      <c r="J125">
-        <v>0</v>
-      </c>
-      <c r="K125">
-        <v>40</v>
-      </c>
-      <c r="L125">
-        <v>0.1736774770610415</v>
-      </c>
-    </row>
-    <row r="126" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B126" t="s">
-        <v>128</v>
-      </c>
-      <c r="C126" t="s">
-        <v>126</v>
-      </c>
-      <c r="D126" t="s">
-        <v>127</v>
-      </c>
-      <c r="E126">
-        <v>2016</v>
-      </c>
-      <c r="F126">
-        <v>1.9300000000000005E-2</v>
-      </c>
-      <c r="G126">
-        <v>1</v>
-      </c>
-      <c r="H126">
-        <v>1336.5</v>
-      </c>
-      <c r="I126">
-        <v>21.450000000000003</v>
-      </c>
-      <c r="J126">
-        <v>0</v>
-      </c>
-      <c r="K126">
-        <v>39</v>
-      </c>
-      <c r="L126">
-        <v>0.17312413828252077</v>
-      </c>
-    </row>
-    <row r="127" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B127" t="s">
-        <v>128</v>
-      </c>
-      <c r="C127" t="s">
-        <v>126</v>
-      </c>
-      <c r="D127" t="s">
-        <v>127</v>
-      </c>
-      <c r="E127">
-        <v>2021</v>
-      </c>
-      <c r="F127">
-        <v>1.1999999999999999E-3</v>
-      </c>
-      <c r="G127">
-        <v>1</v>
-      </c>
-      <c r="H127">
-        <v>1336.5</v>
-      </c>
-      <c r="I127">
-        <v>21.450000000000003</v>
-      </c>
-      <c r="J127">
-        <v>0</v>
-      </c>
-      <c r="K127">
-        <v>34</v>
-      </c>
-      <c r="L127">
-        <v>0.20930892224138253</v>
-      </c>
-    </row>
-    <row r="128" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B128" t="s">
-        <v>129</v>
-      </c>
-      <c r="C128" t="s">
-        <v>130</v>
-      </c>
-      <c r="D128" t="s">
-        <v>131</v>
-      </c>
-      <c r="E128">
-        <v>2010</v>
-      </c>
-      <c r="F128">
-        <v>1.6E-2</v>
-      </c>
-      <c r="G128">
-        <v>0.33123000000000002</v>
-      </c>
-      <c r="L128">
-        <v>0.15124373474020081</v>
-      </c>
-    </row>
-    <row r="129" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B129" t="s">
-        <v>129</v>
-      </c>
-      <c r="C129" t="s">
-        <v>130</v>
-      </c>
-      <c r="D129" t="s">
-        <v>131</v>
-      </c>
-      <c r="E129">
-        <v>2015</v>
-      </c>
-      <c r="F129">
-        <v>1.2E-2</v>
-      </c>
-      <c r="G129">
-        <v>0.33123000000000002</v>
-      </c>
-      <c r="L129">
-        <v>2.2632488991967802E-2</v>
-      </c>
-    </row>
-    <row r="130" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B130" t="s">
-        <v>129</v>
-      </c>
-      <c r="C130" t="s">
-        <v>130</v>
-      </c>
-      <c r="D130" t="s">
-        <v>131</v>
-      </c>
-      <c r="E130">
-        <v>2016</v>
-      </c>
-      <c r="F130">
-        <v>1.2999999999999999E-2</v>
-      </c>
-      <c r="G130">
-        <v>0.33123000000000002</v>
-      </c>
-      <c r="L130">
-        <v>0.15124373474020081</v>
-      </c>
-    </row>
-    <row r="131" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B131" t="s">
-        <v>129</v>
-      </c>
-      <c r="C131" t="s">
-        <v>130</v>
-      </c>
-      <c r="D131" t="s">
-        <v>131</v>
-      </c>
-      <c r="E131">
-        <v>2022</v>
-      </c>
-      <c r="F131">
-        <v>4.6999999999999993E-2</v>
-      </c>
-      <c r="G131">
-        <v>0.33123000000000002</v>
-      </c>
-      <c r="L131">
-        <v>0.12712443086902631</v>
-      </c>
-    </row>
-    <row r="132" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B132" t="s">
-        <v>129</v>
-      </c>
-      <c r="C132" t="s">
-        <v>130</v>
-      </c>
-      <c r="D132" t="s">
-        <v>131</v>
-      </c>
-      <c r="E132">
-        <v>2023</v>
-      </c>
-      <c r="F132">
-        <v>1.4E-2</v>
-      </c>
-      <c r="G132">
-        <v>0.33123000000000002</v>
-      </c>
-      <c r="L132">
         <v>0.18337776500373579</v>
       </c>
     </row>

--- a/VerveStacks_CHE/vt_vervestacks_CHE_v1.xlsx
+++ b/VerveStacks_CHE/vt_vervestacks_CHE_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{779A3ECB-15A7-4E31-982F-5FAA010C5697}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F4024B3E-064A-49C7-8738-7CAEAF900BA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{9A1C369A-C625-4CA0-91A6-F3844E1B062B}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{D3AEBCB6-A68C-432C-A80E-229238358E8D}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -1187,7 +1187,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBC16623-6299-4454-85FA-8F168720885C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC8E93D3-04BC-435B-B20F-578EE0B1319D}">
   <dimension ref="B9:T21"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1877,7 +1877,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DABA996F-C217-4655-8A8F-DBFDB8DED905}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93ED8618-6A9E-4D14-98D2-D6A4E575AC2B}">
   <dimension ref="B9:T122"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_CHE/vt_vervestacks_CHE_v1.xlsx
+++ b/VerveStacks_CHE/vt_vervestacks_CHE_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F4024B3E-064A-49C7-8738-7CAEAF900BA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C1D71DEE-7574-4636-B281-BDC9283A1159}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{D3AEBCB6-A68C-432C-A80E-229238358E8D}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{FFE3BE8E-FDFA-41B7-9FF5-4FA75696C0C4}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -1187,7 +1187,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC8E93D3-04BC-435B-B20F-578EE0B1319D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01988B03-4EEA-470B-9C51-5E2B4DB646D5}">
   <dimension ref="B9:T21"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1266,7 +1266,7 @@
         <v>14</v>
       </c>
       <c r="E11">
-        <v>0.46865000000000007</v>
+        <v>0.4311580000000001</v>
       </c>
       <c r="F11">
         <v>1365</v>
@@ -1322,7 +1322,7 @@
         <v>14</v>
       </c>
       <c r="E12">
-        <v>0.36951250000000002</v>
+        <v>0.33995150000000007</v>
       </c>
       <c r="F12">
         <v>1365</v>
@@ -1378,7 +1378,7 @@
         <v>14</v>
       </c>
       <c r="E13">
-        <v>0.52272499999999988</v>
+        <v>0.48090699999999997</v>
       </c>
       <c r="F13">
         <v>1365</v>
@@ -1434,7 +1434,7 @@
         <v>14</v>
       </c>
       <c r="E14">
-        <v>0.27938750000000001</v>
+        <v>0.25703650000000006</v>
       </c>
       <c r="F14">
         <v>1365</v>
@@ -1490,7 +1490,7 @@
         <v>14</v>
       </c>
       <c r="E15">
-        <v>0.27938750000000001</v>
+        <v>0.25703650000000006</v>
       </c>
       <c r="F15">
         <v>1365</v>
@@ -1546,7 +1546,7 @@
         <v>14</v>
       </c>
       <c r="E16">
-        <v>0.27938750000000001</v>
+        <v>0.25703650000000006</v>
       </c>
       <c r="F16">
         <v>1365</v>
@@ -1602,7 +1602,7 @@
         <v>14</v>
       </c>
       <c r="E17">
-        <v>0.27938750000000001</v>
+        <v>0.25703650000000006</v>
       </c>
       <c r="F17">
         <v>1365</v>
@@ -1658,7 +1658,7 @@
         <v>14</v>
       </c>
       <c r="E18">
-        <v>0.27938750000000001</v>
+        <v>0.25703650000000006</v>
       </c>
       <c r="F18">
         <v>1365</v>
@@ -1714,7 +1714,7 @@
         <v>14</v>
       </c>
       <c r="E19">
-        <v>0.27938750000000001</v>
+        <v>0.25703650000000006</v>
       </c>
       <c r="F19">
         <v>1365</v>
@@ -1770,7 +1770,7 @@
         <v>14</v>
       </c>
       <c r="E20">
-        <v>0.27938750000000001</v>
+        <v>0.25703650000000006</v>
       </c>
       <c r="F20">
         <v>1365</v>
@@ -1826,7 +1826,7 @@
         <v>14</v>
       </c>
       <c r="E21">
-        <v>0.27938750000000001</v>
+        <v>0.25703650000000006</v>
       </c>
       <c r="F21">
         <v>1365</v>
@@ -1877,7 +1877,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93ED8618-6A9E-4D14-98D2-D6A4E575AC2B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93BF5C92-F0B9-4289-BEAF-70006DED2356}">
   <dimension ref="B9:T122"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1962,7 +1962,7 @@
         <v>0.23</v>
       </c>
       <c r="G11">
-        <v>0.33990000000000004</v>
+        <v>0.31270800000000004</v>
       </c>
       <c r="H11">
         <v>4427.5</v>
@@ -2015,7 +2015,7 @@
         <v>0.13120000000000001</v>
       </c>
       <c r="G12">
-        <v>0.59739999999999993</v>
+        <v>0.54960799999999999</v>
       </c>
       <c r="H12">
         <v>1265</v>
@@ -2068,7 +2068,7 @@
         <v>5.5E-2</v>
       </c>
       <c r="G13">
-        <v>0.53560000000000008</v>
+        <v>0.49275200000000008</v>
       </c>
       <c r="H13">
         <v>1265</v>
@@ -2121,7 +2121,7 @@
         <v>4.3799999999999999E-2</v>
       </c>
       <c r="G14">
-        <v>0.42230000000000001</v>
+        <v>0.38851600000000008</v>
       </c>
       <c r="H14">
         <v>1485.0000000000002</v>
@@ -2174,7 +2174,7 @@
         <v>3.1300000000000001E-2</v>
       </c>
       <c r="G15">
-        <v>0.31930000000000003</v>
+        <v>0.29375600000000002</v>
       </c>
       <c r="H15">
         <v>1188</v>
@@ -2227,7 +2227,7 @@
         <v>3.1300000000000001E-2</v>
       </c>
       <c r="G16">
-        <v>0.31930000000000003</v>
+        <v>0.29375600000000002</v>
       </c>
       <c r="H16">
         <v>1188</v>
@@ -2280,7 +2280,7 @@
         <v>3.1300000000000001E-2</v>
       </c>
       <c r="G17">
-        <v>0.31930000000000003</v>
+        <v>0.29375600000000002</v>
       </c>
       <c r="H17">
         <v>1188</v>
@@ -2333,7 +2333,7 @@
         <v>3.1300000000000001E-2</v>
       </c>
       <c r="G18">
-        <v>0.31930000000000003</v>
+        <v>0.29375600000000002</v>
       </c>
       <c r="H18">
         <v>1188</v>
@@ -2386,7 +2386,7 @@
         <v>3.1300000000000001E-2</v>
       </c>
       <c r="G19">
-        <v>0.31930000000000003</v>
+        <v>0.29375600000000002</v>
       </c>
       <c r="H19">
         <v>1188</v>
@@ -2439,7 +2439,7 @@
         <v>3.1300000000000001E-2</v>
       </c>
       <c r="G20">
-        <v>0.31930000000000003</v>
+        <v>0.29375600000000002</v>
       </c>
       <c r="H20">
         <v>1188</v>
@@ -2492,7 +2492,7 @@
         <v>3.1300000000000001E-2</v>
       </c>
       <c r="G21">
-        <v>0.31930000000000003</v>
+        <v>0.29375600000000002</v>
       </c>
       <c r="H21">
         <v>1188</v>
@@ -2545,7 +2545,7 @@
         <v>3.1300000000000001E-2</v>
       </c>
       <c r="G22">
-        <v>0.31930000000000003</v>
+        <v>0.29375600000000002</v>
       </c>
       <c r="H22">
         <v>1188</v>

--- a/VerveStacks_CHE/vt_vervestacks_CHE_v1.xlsx
+++ b/VerveStacks_CHE/vt_vervestacks_CHE_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C1D71DEE-7574-4636-B281-BDC9283A1159}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AD324DCE-24F0-431E-B555-CC984A651C3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{FFE3BE8E-FDFA-41B7-9FF5-4FA75696C0C4}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{CABA0B48-C8C3-498C-935E-806E660962CD}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -1187,7 +1187,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01988B03-4EEA-470B-9C51-5E2B4DB646D5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEA174A0-4013-4816-9504-37DC679E440A}">
   <dimension ref="B9:T21"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1877,7 +1877,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93BF5C92-F0B9-4289-BEAF-70006DED2356}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2166C5B0-3A32-45E5-9A4B-BF6AA601C99F}">
   <dimension ref="B9:T122"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_CHE/vt_vervestacks_CHE_v1.xlsx
+++ b/VerveStacks_CHE/vt_vervestacks_CHE_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AD324DCE-24F0-431E-B555-CC984A651C3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AB5C09B4-2317-47BD-8ABD-E3E62B88976D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{CABA0B48-C8C3-498C-935E-806E660962CD}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{9FA05750-83AA-4888-9234-D20B6349F7F8}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -1187,7 +1187,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEA174A0-4013-4816-9504-37DC679E440A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B7B7F81-D143-455D-91CA-771B6AD6EB82}">
   <dimension ref="B9:T21"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1877,7 +1877,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2166C5B0-3A32-45E5-9A4B-BF6AA601C99F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F1EB708-C8B1-490D-9502-2E92264474B0}">
   <dimension ref="B9:T122"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_CHE/vt_vervestacks_CHE_v1.xlsx
+++ b/VerveStacks_CHE/vt_vervestacks_CHE_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AB5C09B4-2317-47BD-8ABD-E3E62B88976D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E2B01622-6136-4133-A1EC-14E4CA3D516E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{9FA05750-83AA-4888-9234-D20B6349F7F8}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{5802AD69-08D3-4CEA-8BD8-3D300FCFC6E4}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -1187,7 +1187,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B7B7F81-D143-455D-91CA-771B6AD6EB82}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CE0D471-7CD8-4818-8884-0175C784C52F}">
   <dimension ref="B9:T21"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1877,7 +1877,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F1EB708-C8B1-490D-9502-2E92264474B0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72BDEC52-C9E7-4CC4-80C8-60BC25525279}">
   <dimension ref="B9:T122"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_CHE/vt_vervestacks_CHE_v1.xlsx
+++ b/VerveStacks_CHE/vt_vervestacks_CHE_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E2B01622-6136-4133-A1EC-14E4CA3D516E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{389629CF-288F-4307-857E-E97834A13FE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{5802AD69-08D3-4CEA-8BD8-3D300FCFC6E4}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{B9143CA4-AE19-4DB6-A74C-E1DEBC660438}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -1187,7 +1187,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CE0D471-7CD8-4818-8884-0175C784C52F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{655ED82D-9435-47E4-A638-A04E0EBEA99C}">
   <dimension ref="B9:T21"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1877,7 +1877,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72BDEC52-C9E7-4CC4-80C8-60BC25525279}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D45E02F2-CA9F-4718-B6C6-DB1FF2468136}">
   <dimension ref="B9:T122"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_CHE/vt_vervestacks_CHE_v1.xlsx
+++ b/VerveStacks_CHE/vt_vervestacks_CHE_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{389629CF-288F-4307-857E-E97834A13FE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{47F5BBA8-15C5-4A0C-8F05-9624E9883B3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{B9143CA4-AE19-4DB6-A74C-E1DEBC660438}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{6986EE57-BEC8-4275-B5B1-2FED987496F6}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -1187,7 +1187,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{655ED82D-9435-47E4-A638-A04E0EBEA99C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B0D67A9-0B37-4365-8B0C-3306D44588E8}">
   <dimension ref="B9:T21"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1877,7 +1877,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D45E02F2-CA9F-4718-B6C6-DB1FF2468136}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0851F661-CB53-4240-B318-AB0606604966}">
   <dimension ref="B9:T122"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_CHE/vt_vervestacks_CHE_v1.xlsx
+++ b/VerveStacks_CHE/vt_vervestacks_CHE_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{47F5BBA8-15C5-4A0C-8F05-9624E9883B3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A7CC0AE8-54A5-4132-9829-7DC94CC63F81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{6986EE57-BEC8-4275-B5B1-2FED987496F6}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{2F165143-730D-49C0-8AF4-F3E2515FCC8C}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -1187,7 +1187,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B0D67A9-0B37-4365-8B0C-3306D44588E8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5AFD8EAA-C84C-4CDE-AD0E-05A6D1C7E1CA}">
   <dimension ref="B9:T21"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1877,7 +1877,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0851F661-CB53-4240-B318-AB0606604966}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A971553-86F4-41AD-A39E-10D3B48B4E62}">
   <dimension ref="B9:T122"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_CHE/vt_vervestacks_CHE_v1.xlsx
+++ b/VerveStacks_CHE/vt_vervestacks_CHE_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A7CC0AE8-54A5-4132-9829-7DC94CC63F81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{885A1456-050F-4CDD-A4C5-B518DD8CEFE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{2F165143-730D-49C0-8AF4-F3E2515FCC8C}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{FE525E5F-A913-4B38-B444-34F3C0870BEE}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -1187,7 +1187,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5AFD8EAA-C84C-4CDE-AD0E-05A6D1C7E1CA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB266BCD-15AB-4022-AD6E-59DAB9F3AB07}">
   <dimension ref="B9:T21"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1877,7 +1877,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A971553-86F4-41AD-A39E-10D3B48B4E62}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C60E0CED-32AC-4F0D-8237-20E0CA6C10F0}">
   <dimension ref="B9:T122"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
